--- a/tests/promocima_test_cases_v3.xlsx
+++ b/tests/promocima_test_cases_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/narcismagrinabalcells/Dropbox/1 - OFICINA/1-PROMOCIMA/02-CAPITAL PRIVADO/30 - Desarrollo/Préstamos/Claude Pro/promocima/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FCE3D2-B959-5E45-98E4-1C2AD37FEFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06323FD-480F-7C44-B6FF-9035A6517AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16480" yWindow="500" windowWidth="27280" windowHeight="26680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="220" yWindow="880" windowWidth="40380" windowHeight="25620" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_Calculo_cuota" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,10 @@
     <sheet name="3_Situacion" sheetId="3" r:id="rId3"/>
     <sheet name="4_KPIs_Dashboard" sheetId="4" r:id="rId4"/>
     <sheet name="5_Instrucciones" sheetId="5" r:id="rId5"/>
+    <sheet name="5_fmt" sheetId="6" r:id="rId6"/>
+    <sheet name="6_Calculos_Aux" sheetId="7" r:id="rId7"/>
+    <sheet name="7_CalendarioCCP" sheetId="8" r:id="rId8"/>
+    <sheet name="8_LineasCCP" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,8 +43,51 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Narcís Magriñá Balcells</author>
+  </authors>
+  <commentList>
+    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{FA3AE73D-51CC-BD46-B5CF-3A6210927CB9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Narcís Magriñá Balcells:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>OJO, esto es incorrecto ya que cada mes se cobrará menos gestión ya que quedará menos principal.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="495">
   <si>
     <t>HOJA 1 — Calendario Teórico. Interés y principal calculados con fórmulas Excel. Coincidencia compara L vs P y M vs Q.</t>
   </si>
@@ -270,18 +317,6 @@
     <t>Completamente amortizado → ≈0</t>
   </si>
   <si>
-    <t>CF4</t>
-  </si>
-  <si>
-    <t>AP 30k + c1-3</t>
-  </si>
-  <si>
-    <t>AP reduce saldo; cuotas sobre saldo menor</t>
-  </si>
-  <si>
-    <t>Aprox — AP cambia el PMT</t>
-  </si>
-  <si>
     <t>HOJA 3 — Situación préstamo. 'al_dia' = no hay cuotas vencidas sin cobrar. 'con_retraso' = hay cuotas vencidas sin cobrar. null = cancelado o judicializado.</t>
   </si>
   <si>
@@ -759,19 +794,10 @@
     <t>Al día</t>
   </si>
   <si>
-    <t>Amortización parcial</t>
-  </si>
-  <si>
     <t>Fecha ini</t>
   </si>
   <si>
     <t>Fecha préstamo</t>
-  </si>
-  <si>
-    <t>Amortizar parcialmente</t>
-  </si>
-  <si>
-    <t>Judicializar</t>
   </si>
   <si>
     <t>Cancelación
@@ -908,27 +934,15 @@
     <t>(Ingresos anuales - Ingr. Partícipes + Gestión + apertura)/(Principal activo - participado activo)</t>
   </si>
   <si>
-    <t>P3.1</t>
-  </si>
-  <si>
-    <t>Se cancela P3 y se crea P3.1 tras amort parcial</t>
-  </si>
-  <si>
     <t>P4 francés (8% 24 meses, 3 cuotas cobradas)</t>
   </si>
   <si>
     <t>Nuevo principal</t>
   </si>
   <si>
-    <t>Francés 3 cuotas cobradas + AP 30k + 3 cuotas cobradas, manteniendo fecha fin</t>
-  </si>
-  <si>
     <t>Nuevos meses</t>
   </si>
   <si>
-    <t>FA1</t>
-  </si>
-  <si>
     <t>Nuev princ</t>
   </si>
   <si>
@@ -941,26 +955,639 @@
     <t>Mes AP</t>
   </si>
   <si>
-    <t>Post-AP: tercara cuota amortizante</t>
-  </si>
-  <si>
     <t>Nueva fecha inicio</t>
   </si>
   <si>
-    <t>Francés paga 3 cuotas + AP de 20000 - cuota 3</t>
+    <t>Judicializar</t>
+  </si>
+  <si>
+    <t>Judicializar tras 3 meses sin pagar</t>
+  </si>
+  <si>
+    <t>HOJA 5 — Funciones de formato: fmt, fmtInt, fmtN, fmtDec</t>
+  </si>
+  <si>
+    <t>Función</t>
+  </si>
+  <si>
+    <t>Entrada (n)</t>
+  </si>
+  <si>
+    <t>Salida esperada</t>
+  </si>
+  <si>
+    <t>F01</t>
+  </si>
+  <si>
+    <t>fmt</t>
+  </si>
+  <si>
+    <t>1.234,56 €</t>
+  </si>
+  <si>
+    <t>Miles con punto, decimales con coma, símbolo €</t>
+  </si>
+  <si>
+    <t>F02</t>
+  </si>
+  <si>
+    <t>-1.234,56 €</t>
+  </si>
+  <si>
+    <t>Negativo</t>
+  </si>
+  <si>
+    <t>F03</t>
+  </si>
+  <si>
+    <t>0,00 €</t>
+  </si>
+  <si>
+    <t>Cero</t>
+  </si>
+  <si>
+    <t>F04</t>
+  </si>
+  <si>
+    <t>1.000.000,00 €</t>
+  </si>
+  <si>
+    <t>Millón</t>
+  </si>
+  <si>
+    <t>F05</t>
+  </si>
+  <si>
+    <t>0,50 €</t>
+  </si>
+  <si>
+    <t>Menos de 1</t>
+  </si>
+  <si>
+    <t>F06</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Null → guion largo</t>
+  </si>
+  <si>
+    <t>F07</t>
+  </si>
+  <si>
+    <t>fmtInt</t>
+  </si>
+  <si>
+    <t>1.235 €</t>
+  </si>
+  <si>
+    <t>Redondea a entero</t>
+  </si>
+  <si>
+    <t>F08</t>
+  </si>
+  <si>
+    <t>1.000.000 €</t>
+  </si>
+  <si>
+    <t>Millón sin decimales</t>
+  </si>
+  <si>
+    <t>F09</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>fmtN</t>
+  </si>
+  <si>
+    <t>1.235</t>
+  </si>
+  <si>
+    <t>Sin € ni decimales</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>-500</t>
+  </si>
+  <si>
+    <t>Negativo sin €</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>F13</t>
+  </si>
+  <si>
+    <t>fmtDec</t>
+  </si>
+  <si>
+    <t>1.234,56</t>
+  </si>
+  <si>
+    <t>Con decimales, sin €</t>
+  </si>
+  <si>
+    <t>F14</t>
+  </si>
+  <si>
+    <t>-1.234,56</t>
+  </si>
+  <si>
+    <t>F15</t>
+  </si>
+  <si>
+    <t>HOJA 6 — Funciones auxiliares: calcInteresOrdinario, calcInteresesDemora, getLTV</t>
+  </si>
+  <si>
+    <t>Parámetros</t>
+  </si>
+  <si>
+    <t>Fórmula</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>calcInteresOrdinario</t>
+  </si>
+  <si>
+    <t>importe=100000, tasa=6</t>
+  </si>
+  <si>
+    <t>100000 × 6% / 12</t>
+  </si>
+  <si>
+    <t>Interés mensual americano estándar</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>importe=60000, tasa=8</t>
+  </si>
+  <si>
+    <t>60000 × 8% / 12</t>
+  </si>
+  <si>
+    <t>Francés primer mes</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>importe=80000, tasa=9</t>
+  </si>
+  <si>
+    <t>80000 × 9% / 12</t>
+  </si>
+  <si>
+    <t>Americano 9%</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>importe=50000, tasa=0</t>
+  </si>
+  <si>
+    <t>50000 × 0% / 12</t>
+  </si>
+  <si>
+    <t>Tasa cero</t>
+  </si>
+  <si>
+    <t>D01</t>
+  </si>
+  <si>
+    <t>calcInteresesDemora</t>
+  </si>
+  <si>
+    <t>importe=10000, tasa=14, dias=30</t>
+  </si>
+  <si>
+    <t>10000×14%/365×30</t>
+  </si>
+  <si>
+    <t>Un mes de demora aprox</t>
+  </si>
+  <si>
+    <t>D02</t>
+  </si>
+  <si>
+    <t>importe=10000, tasa=14, dias=0</t>
+  </si>
+  <si>
+    <t>10000×14%/365×0</t>
+  </si>
+  <si>
+    <t>Cero días</t>
+  </si>
+  <si>
+    <t>D03</t>
+  </si>
+  <si>
+    <t>importe=10000, tasa=14, dias=365</t>
+  </si>
+  <si>
+    <t>10000×14%/365×365</t>
+  </si>
+  <si>
+    <t>Un año exacto</t>
+  </si>
+  <si>
+    <t>D04</t>
+  </si>
+  <si>
+    <t>importe=50000, tasa=10, dias=90</t>
+  </si>
+  <si>
+    <t>50000×10%/365×90</t>
+  </si>
+  <si>
+    <t>90 días</t>
+  </si>
+  <si>
+    <t>L01</t>
+  </si>
+  <si>
+    <t>getLTV</t>
+  </si>
+  <si>
+    <t>{importe:100000}, {valor_tasacion:200000}</t>
+  </si>
+  <si>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>100000/200000×100</t>
+  </si>
+  <si>
+    <t>LTV 50%</t>
+  </si>
+  <si>
+    <t>L02</t>
+  </si>
+  <si>
+    <t>{importe:80000},  {valor_tasacion:300000}</t>
+  </si>
+  <si>
+    <t>26.7</t>
+  </si>
+  <si>
+    <t>80000/300000×100</t>
+  </si>
+  <si>
+    <t>LTV 26.7%</t>
+  </si>
+  <si>
+    <t>L03</t>
+  </si>
+  <si>
+    <t>{importe:100000}, garantia=null</t>
+  </si>
+  <si>
+    <t>Sin garantía → null</t>
+  </si>
+  <si>
+    <t>HOJA 7 — generateCalendarioCCP: calendario de cuotas del partícipe</t>
+  </si>
+  <si>
+    <t>Préstamo base: Americano 100k 6% 12m inicio 2024-01-15 día 15 | IRPF 19% | Gestión 2% | Participación 40% (importe 40.000€) | Fórmulas: Beneficio = 40000 × 6%/12 × factor   Gestión = 40000 × 2%/12 × factor   Bruto = Beneficio - Gestión   IRPF = Bruto × 19%   Neto = Bruto - IRPF</t>
+  </si>
+  <si>
+    <t>fecha_firma contrato</t>
+  </si>
+  <si>
+    <t>fecha_prestamo esperada</t>
+  </si>
+  <si>
+    <t>Factor esperado</t>
+  </si>
+  <si>
+    <t>Beneficio esperado</t>
+  </si>
+  <si>
+    <t>Gestión esperada</t>
+  </si>
+  <si>
+    <t>Neto esperado</t>
+  </si>
+  <si>
+    <t>CC1-a</t>
+  </si>
+  <si>
+    <t>Firma mismo día cobro (día 15) → factor=1 c1</t>
+  </si>
+  <si>
+    <t>2024-02-15</t>
+  </si>
+  <si>
+    <t>diaFirma=diaCobro → factor=1</t>
+  </si>
+  <si>
+    <t>CC1-b</t>
+  </si>
+  <si>
+    <t>Firma mismo día cobro → c2 también factor=1</t>
+  </si>
+  <si>
+    <t>2024-03-15</t>
+  </si>
+  <si>
+    <t>cuota 2 siempre factor=1 si firma&lt;=diaCobro</t>
+  </si>
+  <si>
+    <t>CC1-c</t>
+  </si>
+  <si>
+    <t>Firma mismo día cobro → última cuota (c12)</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>cuota 12 factor=1</t>
+  </si>
+  <si>
+    <t>CC2-a</t>
+  </si>
+  <si>
+    <t>Firma día 5, cobro día 15 → factor=(15-5)/30=0.333</t>
+  </si>
+  <si>
+    <t>2024-01-05</t>
+  </si>
+  <si>
+    <t>factor=(15-5)/30</t>
+  </si>
+  <si>
+    <t>CC2-b</t>
+  </si>
+  <si>
+    <t>Firma día 5, cobro día 15 → c2 factor=1</t>
+  </si>
+  <si>
+    <t>diaFirma(5)&lt;=diaCobro(15) → c2=1</t>
+  </si>
+  <si>
+    <t>CC3-a</t>
+  </si>
+  <si>
+    <t>Firma día 20, cobro día 15 → c1 omitida (factor=0)</t>
+  </si>
+  <si>
+    <t>2024-02-20</t>
+  </si>
+  <si>
+    <t>factor=0 → cuota omitida del calendario</t>
+  </si>
+  <si>
+    <t>CC3-b</t>
+  </si>
+  <si>
+    <t>Firma día 20, cobro día 15 → c2 factor=(30-20+15)/30=0.833</t>
+  </si>
+  <si>
+    <t>2024-04-15</t>
+  </si>
+  <si>
+    <t>factor=(30-20+15)/30</t>
+  </si>
+  <si>
+    <t>CC3-c</t>
+  </si>
+  <si>
+    <t>Firma día 20, cobro día 15 → c3 factor=1</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>cuota 3+ siempre factor=1</t>
+  </si>
+  <si>
+    <t>CC4-a</t>
+  </si>
+  <si>
+    <t>Firma 2024-06-15 (c5 del préstamo) → primera cuota del partícipe</t>
+  </si>
+  <si>
+    <t>2024-06-15</t>
+  </si>
+  <si>
+    <t>2024-07-15</t>
+  </si>
+  <si>
+    <t>firma coincide con día cobro → factor=1</t>
+  </si>
+  <si>
+    <t>CC4-b</t>
+  </si>
+  <si>
+    <t>Firma 2024-06-15 → cuota 6 del préstamo es c2 del partícipe</t>
+  </si>
+  <si>
+    <t>2024-08-15</t>
+  </si>
+  <si>
+    <t>cuota 2+ factor=1</t>
+  </si>
+  <si>
+    <t>HOJA 8 — calcularLineasCCP: estado de cada línea del calendario del partícipe</t>
+  </si>
+  <si>
+    <t>Interés</t>
+  </si>
+  <si>
+    <t>Fecha firma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestión </t>
+  </si>
+  <si>
+    <t>IRPF</t>
+  </si>
+  <si>
+    <t>Cobro mensual</t>
+  </si>
+  <si>
+    <t>Pago mensual</t>
+  </si>
+  <si>
+    <t>Gestión mensual</t>
+  </si>
+  <si>
+    <t>Bruto</t>
+  </si>
+  <si>
+    <t>Neto</t>
+  </si>
+  <si>
+    <t>Dataset fijo: Americano 100k 6% 12m inicio 2024-01-15 día 15 | CCP: firma 2024-01-15, participación 40% (40.000€), gestión 2%, IRPF 19% | Neto cuota completa = 108€  (beneficio 200 - gestión 66.67 = bruto 133.33 - IRPF 25.33 = 108)</t>
+  </si>
+  <si>
+    <t>Cobros préstamo</t>
+  </si>
+  <si>
+    <t>Pagos partícipe</t>
+  </si>
+  <si>
+    <t>col_pendiente</t>
+  </si>
+  <si>
+    <t>col_devengado</t>
+  </si>
+  <si>
+    <t>col_pagado</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Sin cobros → todo pendiente</t>
+  </si>
+  <si>
+    <t>Sin pagos</t>
+  </si>
+  <si>
+    <t>pendiente</t>
+  </si>
+  <si>
+    <t>Préstamo no ha cobrado nada</t>
+  </si>
+  <si>
+    <t>Sin cobros → todo pendiente (c3)</t>
+  </si>
+  <si>
+    <t>Mismo para cualquier cuota sin cobro</t>
+  </si>
+  <si>
+    <t>Cuota 1 cobrada, sin pago partícipe → devengado</t>
+  </si>
+  <si>
+    <t>c1 cobrada (500€ interés)</t>
+  </si>
+  <si>
+    <t>devengado</t>
+  </si>
+  <si>
+    <t>El préstamo cobró, el partícipe no ha recibido nada</t>
+  </si>
+  <si>
+    <t>L04</t>
+  </si>
+  <si>
+    <t>Cuotas 1-3 cobradas, sin pago → todas devengadas</t>
+  </si>
+  <si>
+    <t>c1,c2,c3 cobradas</t>
+  </si>
+  <si>
+    <t>Cuota 2 también devengada</t>
+  </si>
+  <si>
+    <t>L05</t>
+  </si>
+  <si>
+    <t>Cuota 1 cobrada y pagada al partícipe</t>
+  </si>
+  <si>
+    <t>c1 cobrada</t>
+  </si>
+  <si>
+    <t>Pago 108€</t>
+  </si>
+  <si>
+    <t>pagado</t>
+  </si>
+  <si>
+    <t>Pago cubre exactamente el neto</t>
+  </si>
+  <si>
+    <t>L06</t>
+  </si>
+  <si>
+    <t>Cuota 1 cobrada, pago parcial 50€</t>
+  </si>
+  <si>
+    <t>Pago 50€</t>
+  </si>
+  <si>
+    <t>mixto</t>
+  </si>
+  <si>
+    <t>col_devengado = 108-50 = 58</t>
+  </si>
+  <si>
+    <t>L07</t>
+  </si>
+  <si>
+    <t>c1 y c2 cobradas, pago 108€ → c1 pagada c2 devengada</t>
+  </si>
+  <si>
+    <t>c1 y c2 cobradas</t>
+  </si>
+  <si>
+    <t>El pago cubre c1 completa</t>
+  </si>
+  <si>
+    <t>L08</t>
+  </si>
+  <si>
+    <t>Pool agotado en c1, c2 queda devengada</t>
+  </si>
+  <si>
+    <t>L09</t>
+  </si>
+  <si>
+    <t>c1 y c2 cobradas, pago 216€ → ambas pagadas</t>
+  </si>
+  <si>
+    <t>Pago 216€</t>
+  </si>
+  <si>
+    <t>Pago 216 = 2 × 108</t>
+  </si>
+  <si>
+    <t>L10</t>
+  </si>
+  <si>
+    <t>c1 y c2 cobradas, pago 216€ → c2 también pagada</t>
+  </si>
+  <si>
+    <t>Pool cubre ambas</t>
+  </si>
+  <si>
+    <t>L11</t>
+  </si>
+  <si>
+    <t>c1 cobrada solo a medias (250€ de 500€) → ratio 0.5 → col_devengado=54</t>
+  </si>
+  <si>
+    <t>c1 cobrada 250€ (50% del interés)</t>
+  </si>
+  <si>
+    <t>ratio=0.5 → neto_cobrado=54, pendiente=54</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ _€;[Red]\-#,##0.00\ _€"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1218,8 +1845,61 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="45">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1467,8 +2147,34 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FFE9F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1621,7 +2327,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1677,8 +2383,11 @@
     <xf numFmtId="14" fontId="13" fillId="43" borderId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="38" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1839,9 +2548,6 @@
     <xf numFmtId="0" fontId="32" fillId="39" borderId="0" xfId="43" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="37" borderId="0" xfId="41" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="37" borderId="0" xfId="41" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1937,143 +2643,162 @@
     <xf numFmtId="3" fontId="4" fillId="36" borderId="0" xfId="42" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="4" fillId="36" borderId="11" xfId="42" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="32" fillId="39" borderId="12" xfId="43" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="36" borderId="11" xfId="42" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="36" borderId="0" xfId="47" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="32" fillId="39" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="38" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="36" borderId="11" xfId="42" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="39" borderId="12" xfId="43" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="44" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="44" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="36" borderId="11" xfId="42" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="36" borderId="0" xfId="47" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="32" fillId="39" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="44" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="45" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="45" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="37" borderId="0" xfId="41" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="40" fillId="46" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="36" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="32" fillId="39" borderId="0" xfId="43" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="39" borderId="0" xfId="43" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="26" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="36" borderId="0" xfId="42" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="39" borderId="0" xfId="43" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="32" fillId="39" borderId="0" xfId="43" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="47" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="47" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="48" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" xfId="50"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="42" fillId="49" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="26" fillId="37" borderId="0" xfId="41" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="26" fillId="37" borderId="0" xfId="41" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="26" fillId="37" borderId="0" xfId="41" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="36" borderId="0" xfId="42" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="36" borderId="0" xfId="42" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" xfId="41" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="52">
     <cellStyle name="20% - Énfasis1" xfId="18" builtinId="30" hidden="1"/>
     <cellStyle name="20% - Énfasis2" xfId="22" builtinId="34" hidden="1"/>
     <cellStyle name="20% - Énfasis3" xfId="26" builtinId="38" hidden="1"/>
@@ -2101,6 +2826,7 @@
     <cellStyle name="Encabezado 1" xfId="6" builtinId="16" hidden="1"/>
     <cellStyle name="Encabezado 4" xfId="9" builtinId="19" hidden="1"/>
     <cellStyle name="Énfasis1" xfId="17" builtinId="29" hidden="1"/>
+    <cellStyle name="Énfasis1" xfId="50" builtinId="29"/>
     <cellStyle name="Énfasis2" xfId="21" builtinId="33" hidden="1"/>
     <cellStyle name="Énfasis3" xfId="25" builtinId="37" hidden="1"/>
     <cellStyle name="Énfasis4" xfId="29" builtinId="41" hidden="1"/>
@@ -2111,10 +2837,12 @@
     <cellStyle name="Millares" xfId="1" builtinId="3" hidden="1"/>
     <cellStyle name="Millares" xfId="47" builtinId="3"/>
     <cellStyle name="Millares [0]" xfId="3" builtinId="6" hidden="1"/>
+    <cellStyle name="Millares 2" xfId="51" xr:uid="{112266F0-16F9-F04C-B73B-CC2404AD47CC}"/>
     <cellStyle name="Moneda [0]" xfId="4" builtinId="7" hidden="1"/>
     <cellStyle name="Neutral" xfId="46" builtinId="28" hidden="1"/>
     <cellStyle name="No aplica" xfId="48" xr:uid="{924E9B81-CBD7-AE46-A5D2-FB323350DC8B}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="49" xr:uid="{1775F775-4DBA-824A-B436-5876693B3095}"/>
     <cellStyle name="Notas" xfId="15" builtinId="10" hidden="1"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
     <cellStyle name="Referencia" xfId="43" xr:uid="{116AED6D-C992-2440-8C3C-3D941E3A09DF}"/>
@@ -2893,8 +3621,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D6982061-47A7-CF4D-BCC3-ACCB0A54F302}" name="T_Prestamos" displayName="T_Prestamos" ref="A7:Q12" totalsRowShown="0" headerRowDxfId="56">
-  <autoFilter ref="A7:Q12" xr:uid="{D6982061-47A7-CF4D-BCC3-ACCB0A54F302}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D6982061-47A7-CF4D-BCC3-ACCB0A54F302}" name="T_Prestamos" displayName="T_Prestamos" ref="A7:Q11" totalsRowShown="0" headerRowDxfId="56">
+  <autoFilter ref="A7:Q11" xr:uid="{D6982061-47A7-CF4D-BCC3-ACCB0A54F302}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{641D8D61-447C-6641-AB5E-73CCB1A3E849}" name="Ref" dataDxfId="55"/>
     <tableColumn id="2" xr3:uid="{E35DC7D9-5ECA-8540-910A-3C9E80A32E82}" name="Descripción" dataDxfId="54"/>
@@ -2929,22 +3657,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1E9135F6-C264-9E4A-A876-A4EFA5CA18A6}" name="T_CCP" displayName="T_CCP" ref="A16:R19" totalsRowShown="0" headerRowDxfId="38">
-  <autoFilter ref="A16:R19" xr:uid="{1E9135F6-C264-9E4A-A876-A4EFA5CA18A6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1E9135F6-C264-9E4A-A876-A4EFA5CA18A6}" name="T_CCP" displayName="T_CCP" ref="A15:R18" totalsRowShown="0" headerRowDxfId="38">
+  <autoFilter ref="A15:R18" xr:uid="{1E9135F6-C264-9E4A-A876-A4EFA5CA18A6}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{2FF2B3C2-B2DD-6642-B8A7-953EC30996E0}" name="Ref" dataDxfId="37" dataCellStyle="Dato"/>
     <tableColumn id="2" xr3:uid="{828D80FF-C75B-0F49-80A8-36BFF259CA03}" name="Descripción" dataDxfId="36" dataCellStyle="Dato"/>
     <tableColumn id="3" xr3:uid="{6E5D2940-1188-F041-9F72-F8EAD8CDC2B6}" name="Préstamo" dataDxfId="35" dataCellStyle="Dato"/>
     <tableColumn id="4" xr3:uid="{C5E5662B-67C6-E145-823B-BE159B591A6D}" name="% participación" dataDxfId="34" dataCellStyle="Dato"/>
     <tableColumn id="5" xr3:uid="{3680C9A9-B0B8-F243-B5D2-DA152F32DC0C}" name="Participación" dataDxfId="33" dataCellStyle="Cáclculo">
-      <calculatedColumnFormula>L17*D17</calculatedColumnFormula>
+      <calculatedColumnFormula>L16*D16</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{75B4A016-1F54-014F-9858-74B67C9B0009}" name="% gestión" dataDxfId="32" dataCellStyle="Dato"/>
     <tableColumn id="7" xr3:uid="{2649786C-89C8-6847-A0C2-430E8823C1F5}" name="Ingresos anuales" dataDxfId="31" dataCellStyle="Cáclculo">
       <calculatedColumnFormula>T_CCP[[#This Row],[Ingr. Anuales prest.]]*T_CCP[[#This Row],[% participación]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{7BC52623-18E4-ED46-B574-8E48DA700D69}" name="Gestión" dataDxfId="30" dataCellStyle="Cáclculo">
-      <calculatedColumnFormula>IF(T_CCP[[#This Row],[Estado final]]="Activo",E17*F17,0)</calculatedColumnFormula>
+      <calculatedColumnFormula>T_CCP[[#This Row],[Participado final]]*T_CCP[[#This Row],[% gestión]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{A1964C3E-4A3F-0D40-8DC1-C9F5B90077FD}" name="Garantías part." dataDxfId="29" dataCellStyle="Cáclculo">
       <calculatedColumnFormula>T_CCP[[#This Row],[Garantías prestamo]]*T_CCP[[#This Row],[% participación]]</calculatedColumnFormula>
@@ -2953,28 +3681,28 @@
       <calculatedColumnFormula>T_CCP[[#This Row],[Principal final]]*T_CCP[[#This Row],[% participación]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{5346D4B5-ADED-6540-A6F0-0FADC2AA1579}" name="Aux Tasa" dataDxfId="27" dataCellStyle="Porcentaje">
-      <calculatedColumnFormula>VLOOKUP(C17,$A$8:$L$12,$F$5,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(C16,$A$8:$L$11,$F$5,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{9669D734-117F-5E4A-9648-D63F0EF6C2E4}" name="Aux Principal" dataDxfId="26" dataCellStyle="Referencia">
-      <calculatedColumnFormula>VLOOKUP(C17,$A$8:$L$12,$C$5,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(C16,$A$8:$L$11,$C$5,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{C07A9080-EB82-764A-B048-C33A00CB2999}" name="Estado final" dataDxfId="25">
-      <calculatedColumnFormula>IF(VLOOKUP(C17,T_Prestamos[],$L$5,FALSE)=0,"",VLOOKUP(C17,T_Prestamos[],$L$5,FALSE))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(VLOOKUP(C16,T_Prestamos[],$L$5,FALSE)=0,"",VLOOKUP(C16,T_Prestamos[],$L$5,FALSE))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{B836E1A0-F37D-E344-897B-E06FE473C670}" name="Situación final" dataDxfId="24">
-      <calculatedColumnFormula>IF(VLOOKUP(C17,T_Prestamos[],$M$5,FALSE)=0,"",VLOOKUP(C17,T_Prestamos[],$M$5,FALSE))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(VLOOKUP(C16,T_Prestamos[],$M$5,FALSE)=0,"",VLOOKUP(C16,T_Prestamos[],$M$5,FALSE))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{79873CDF-EB18-5748-9E02-9A57CB1E6B3A}" name="Principal final" dataDxfId="23">
-      <calculatedColumnFormula>VLOOKUP(C17,T_Prestamos[],$N$5,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(C16,T_Prestamos[],$N$5,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{B807E56E-21F3-4642-B5EC-AF905C93DC6F}" name="Ingr. Anuales prest." dataDxfId="22" dataCellStyle="Referencia">
-      <calculatedColumnFormula>VLOOKUP(C17,T_Prestamos[],$P$5,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(C16,T_Prestamos[],$P$5,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{1355E25B-22AC-4740-B1B9-787C481E7754}" name="Garantías prestamo" dataDxfId="21" dataCellStyle="Referencia">
-      <calculatedColumnFormula>VLOOKUP(C17,T_Prestamos[],$J$5,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(C16,T_Prestamos[],$J$5,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{DC60337A-9D8B-FC4D-8280-4F58FC026482}" name="Meses" dataDxfId="20" dataCellStyle="Referencia">
-      <calculatedColumnFormula>VLOOKUP(C17,T_Prestamos[],$Q$5,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(C16,T_Prestamos[],$Q$5,FALSE)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2982,49 +3710,49 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{027CEA3A-1AB5-7945-821E-8D1382FCBFBC}" name="T_Acciones_Prestamos" displayName="T_Acciones_Prestamos" ref="A22:S29" totalsRowShown="0" headerRowDxfId="19">
-  <autoFilter ref="A22:S29" xr:uid="{027CEA3A-1AB5-7945-821E-8D1382FCBFBC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{027CEA3A-1AB5-7945-821E-8D1382FCBFBC}" name="T_Acciones_Prestamos" displayName="T_Acciones_Prestamos" ref="A21:S27" totalsRowShown="0" headerRowDxfId="19">
+  <autoFilter ref="A21:S27" xr:uid="{027CEA3A-1AB5-7945-821E-8D1382FCBFBC}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{92637E1D-E1B0-8145-B6B2-362FDC68A430}" name="Préstamo" dataDxfId="18" dataCellStyle="Dato"/>
     <tableColumn id="18" xr3:uid="{CD82B007-2DF3-F54C-9662-93944C73A584}" name="Descripción" dataDxfId="17" dataCellStyle="Dato"/>
     <tableColumn id="2" xr3:uid="{C4783235-36FE-6C48-83FE-AE8C0110F5DA}" name="Orden" dataDxfId="16" dataCellStyle="Dato">
-      <calculatedColumnFormula>IF(A23=A22,C22+1,1)</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(A22=A21,C21+1,1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{BCCE9010-2922-9048-B64A-BAD9CC88FF1C}" name="Cuota_ini" dataDxfId="15" dataCellStyle="Dato"/>
     <tableColumn id="4" xr3:uid="{3308BED9-F919-8D42-90C0-676B468FD32C}" name="Cuota_fin" dataDxfId="14" dataCellStyle="Dato"/>
     <tableColumn id="5" xr3:uid="{55A5ED29-F282-654C-8806-0BB061D8692C}" name="Fecha ini" dataDxfId="13" dataCellStyle="Cáclculo">
-      <calculatedColumnFormula>EDATE(S23,D23)</calculatedColumnFormula>
+      <calculatedColumnFormula>EDATE(S22,D22)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{1CDD32D7-BFC6-D540-8894-191DE4CB8C99}" name="Fecha Fin" dataDxfId="12" dataCellStyle="Cáclculo">
-      <calculatedColumnFormula>EDATE(S23,E23)</calculatedColumnFormula>
+      <calculatedColumnFormula>EDATE(S22,E22)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{FA5FBDF8-32F0-EA4F-B279-E80181AB59EE}" name="Acción" dataDxfId="11" dataCellStyle="Dato"/>
     <tableColumn id="8" xr3:uid="{F95714F0-F67B-8B46-A47B-FE9805AD7228}" name="Intereses" dataDxfId="10">
-      <calculatedColumnFormula>ROUND(IF(Q23="Americano",P23*O23/12*(T_Acciones_Prestamos[[#This Row],[Cuota_fin]]-T_Acciones_Prestamos[[#This Row],[Cuota_ini]]+1),-CUMIPMT(O23/12,R23,P23,D23,E23,0)),2)</calculatedColumnFormula>
+      <calculatedColumnFormula>ROUND(IF(Q22="Americano",P22*O22/12*(T_Acciones_Prestamos[[#This Row],[Cuota_fin]]-T_Acciones_Prestamos[[#This Row],[Cuota_ini]]+1),-CUMIPMT(O22/12,R22,P22,D22,E22,0)),2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{ADCD41DD-DDB8-8B4A-8068-D0243DCE79FE}" name="Principal" dataDxfId="9">
-      <calculatedColumnFormula>ROUND(IF(Q23="Americano",0,-CUMPRINC(O23/12,R23,P23,D23,E23,0)),2)</calculatedColumnFormula>
+      <calculatedColumnFormula>ROUND(IF(Q22="Americano",0,-CUMPRINC(O22/12,R22,P22,D22,E22,0)),2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{6DE90D27-2474-0440-9B4F-3D7C75EFB1D0}" name="Cancelación_x000a_Judicialización_x000a_Amortización parcial" dataDxfId="8" dataCellStyle="Referencia">
-      <calculatedColumnFormula>IF(T_Acciones_Prestamos[[#This Row],[Descripción]]="Cancelación del préstamo",P23,"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(T_Acciones_Prestamos[[#This Row],[Descripción]]="Cancelación del préstamo",P22,"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{D9FD0DCD-352E-FD4F-A691-72FF467E1577}" name="Judicialización" dataDxfId="7" dataCellStyle="Dato"/>
     <tableColumn id="12" xr3:uid="{5872BE42-18DC-6848-ADE0-27462914D4B0}" name="Saldo Principal" dataDxfId="6" dataCellStyle="Cáclculo">
-      <calculatedColumnFormula>P23-J23-K23</calculatedColumnFormula>
+      <calculatedColumnFormula>P22-J22-K22</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{49941383-46F1-954B-8D0C-32EE27CBD8B6}" name="Ing. Anuales" dataDxfId="5" dataCellStyle="Cáclculo"/>
     <tableColumn id="13" xr3:uid="{4DD5F15F-8DF0-DD4E-8201-0F14DC218BB9}" name="Aux Tasa" dataDxfId="4" dataCellStyle="Porcentaje">
-      <calculatedColumnFormula>VLOOKUP(A23,$A$8:$Q$12,$F$5,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(A22,$A$8:$Q$11,$F$5,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{2B41E914-31CE-2348-A100-875E2F416940}" name="Aux Principal" dataDxfId="3" dataCellStyle="Dato"/>
     <tableColumn id="15" xr3:uid="{0C2FB86B-CC5C-F84C-A9DF-8A1660AB437C}" name="Aux Tipo" dataDxfId="2" dataCellStyle="Referencia">
-      <calculatedColumnFormula>VLOOKUP(A23,$A$8:$Q$12,$E$5,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(A22,$A$8:$Q$11,$E$5,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{A3AD0FB4-81B0-D349-8006-60D40AF82400}" name="Aux duración" dataDxfId="1" dataCellStyle="Referencia">
-      <calculatedColumnFormula>VLOOKUP(A23,$A$8:$Q$12,$G$5,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(A22,$A$8:$Q$11,$G$5,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{63E94B19-0F88-E645-9EAA-4B8D00B771C6}" name="Fecha préstamo" dataDxfId="0" dataCellStyle="Referencia">
-      <calculatedColumnFormula>VLOOKUP(A23,$A$8:$Q$12,$D$5,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(A22,$A$8:$Q$11,$D$5,FALSE)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3210,7 +3938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3230,722 +3958,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="137" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="136"/>
-      <c r="R1" s="136"/>
-      <c r="S1" s="136"/>
-      <c r="T1" s="136"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="136" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="136"/>
-      <c r="N2" s="136"/>
-      <c r="O2" s="136"/>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="136"/>
-      <c r="R2" s="136"/>
-      <c r="S2" s="136"/>
-      <c r="T2" s="136"/>
-    </row>
-    <row r="3" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3">
-        <v>100000</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0.06</v>
-      </c>
-      <c r="F4" s="5">
-        <v>12</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="5">
-        <v>15</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="134">
-        <v>45337</v>
-      </c>
-      <c r="L4" s="134"/>
-      <c r="M4" s="134"/>
-      <c r="N4" s="134"/>
-      <c r="O4" s="134"/>
-      <c r="P4" s="134"/>
-      <c r="Q4" s="6">
-        <f>D4*E4/12</f>
-        <v>500</v>
-      </c>
-      <c r="R4" s="6">
-        <f>IF(J4=F4,D4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S4" s="6">
-        <f t="shared" ref="S4:S12" si="0">Q4+R4</f>
-        <v>500</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="8">
-        <v>100000</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="F5" s="10">
-        <v>12</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="10">
-        <v>15</v>
-      </c>
-      <c r="I5" s="10">
-        <v>0</v>
-      </c>
-      <c r="J5" s="10">
-        <v>12</v>
-      </c>
-      <c r="K5" s="134">
-        <v>45672</v>
-      </c>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="11">
-        <f>D5*E5/12</f>
-        <v>500</v>
-      </c>
-      <c r="R5" s="11">
-        <f>IF(J5=F5,D5,0)</f>
-        <v>100000</v>
-      </c>
-      <c r="S5" s="11">
-        <f t="shared" si="0"/>
-        <v>100500</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="3">
-        <v>50000</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.09</v>
-      </c>
-      <c r="F6" s="5">
-        <v>24</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>6</v>
-      </c>
-      <c r="K6" s="134">
-        <v>45536</v>
-      </c>
-      <c r="L6" s="134"/>
-      <c r="M6" s="134"/>
-      <c r="N6" s="134"/>
-      <c r="O6" s="134"/>
-      <c r="P6" s="134"/>
-      <c r="Q6" s="6">
-        <f>D6*E6/12</f>
-        <v>375</v>
-      </c>
-      <c r="R6" s="6">
-        <f>IF(J6=F6,D6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S6" s="6">
-        <f t="shared" si="0"/>
-        <v>375</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="8">
-        <v>100000</v>
-      </c>
-      <c r="E7" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="F7" s="10">
-        <v>12</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="10">
-        <v>15</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0</v>
-      </c>
-      <c r="J7" s="10">
-        <v>1</v>
-      </c>
-      <c r="K7" s="134">
-        <v>45337</v>
-      </c>
-      <c r="L7" s="134"/>
-      <c r="M7" s="134"/>
-      <c r="N7" s="134"/>
-      <c r="O7" s="134"/>
-      <c r="P7" s="134"/>
-      <c r="Q7" s="11">
-        <f>-CUMIPMT(E7/12,F7,D7,J7,J7,0)</f>
-        <v>500</v>
-      </c>
-      <c r="R7" s="11">
-        <f>-CUMPRINC(E7/12,F7,D7,J7,J7,0)</f>
-        <v>8106.6429707080642</v>
-      </c>
-      <c r="S7" s="11">
-        <f t="shared" si="0"/>
-        <v>8606.6429707080642</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="3">
-        <v>100000</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0.06</v>
-      </c>
-      <c r="F8" s="5">
-        <v>12</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="5">
-        <v>15</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
-        <v>6</v>
-      </c>
-      <c r="K8" s="134">
-        <v>45488</v>
-      </c>
-      <c r="L8" s="134"/>
-      <c r="M8" s="134"/>
-      <c r="N8" s="134"/>
-      <c r="O8" s="134"/>
-      <c r="P8" s="134"/>
-      <c r="Q8" s="6">
-        <f>-CUMIPMT(E8/12,F8,D8,J8,J8,0)</f>
-        <v>295.29710632731621</v>
-      </c>
-      <c r="R8" s="6">
-        <f>-CUMPRINC(E8/12,F8,D8,J8,J8,0)</f>
-        <v>8311.345864380748</v>
-      </c>
-      <c r="S8" s="6">
-        <f t="shared" si="0"/>
-        <v>8606.6429707080642</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="8">
-        <v>100000</v>
-      </c>
-      <c r="E9" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="F9" s="10">
-        <v>12</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="10">
-        <v>15</v>
-      </c>
-      <c r="I9" s="10">
-        <v>0</v>
-      </c>
-      <c r="J9" s="10">
-        <v>12</v>
-      </c>
-      <c r="K9" s="134">
-        <v>45672</v>
-      </c>
-      <c r="L9" s="134"/>
-      <c r="M9" s="134"/>
-      <c r="N9" s="134"/>
-      <c r="O9" s="134"/>
-      <c r="P9" s="134"/>
-      <c r="Q9" s="11">
-        <f>-CUMIPMT(E9/12,F9,D9,J9,J9,0)</f>
-        <v>42.819119257253988</v>
-      </c>
-      <c r="R9" s="11">
-        <f>-CUMPRINC(E9/12,F9,D9,J9,J9,0)</f>
-        <v>8563.8238514508103</v>
-      </c>
-      <c r="S9" s="11">
-        <f t="shared" si="0"/>
-        <v>8606.6429707080642</v>
-      </c>
-      <c r="T9" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="3">
-        <v>60000</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0.08</v>
-      </c>
-      <c r="F10" s="5">
-        <v>24</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="5">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <v>1</v>
-      </c>
-      <c r="K10" s="134">
-        <v>45474</v>
-      </c>
-      <c r="L10" s="134"/>
-      <c r="M10" s="134"/>
-      <c r="N10" s="134"/>
-      <c r="O10" s="134"/>
-      <c r="P10" s="134"/>
-      <c r="Q10" s="6">
-        <f>-CUMIPMT(E10/12,F10,D10,J10,J10,0)</f>
-        <v>400.00000000000045</v>
-      </c>
-      <c r="R10" s="6">
-        <f>-CUMPRINC(E10/12,F10,D10,J10,J10,0)</f>
-        <v>2313.6374873710488</v>
-      </c>
-      <c r="S10" s="6">
-        <f t="shared" si="0"/>
-        <v>2713.6374873710492</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="8">
-        <v>80000</v>
-      </c>
-      <c r="E11" s="9">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F11" s="10">
-        <v>18</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="10">
-        <v>1</v>
-      </c>
-      <c r="I11" s="10">
-        <v>6</v>
-      </c>
-      <c r="J11" s="10">
-        <v>1</v>
-      </c>
-      <c r="K11" s="134">
-        <v>45323</v>
-      </c>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
-      <c r="N11" s="134"/>
-      <c r="O11" s="134"/>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="6">
-        <f>IF(J11&lt;=I11,D11*E11/12,-ROUND(CUMIPMT(E11/12,F11-I11,D11,J11-I11,J11-I11,0),2))</f>
-        <v>466.66666666666674</v>
-      </c>
-      <c r="R11" s="6">
-        <f>IF(J11&lt;=I11,0,-ROUND(CUMPRINC(E11/12,F11-I11,D11,J11-I11,J11-I11,0),2))</f>
-        <v>0</v>
-      </c>
-      <c r="S11" s="11">
-        <f t="shared" si="0"/>
-        <v>466.66666666666674</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="3">
-        <v>80000</v>
-      </c>
-      <c r="E12" s="4">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F12" s="5">
-        <v>18</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" s="5">
-        <v>1</v>
-      </c>
-      <c r="I12" s="5">
-        <v>6</v>
-      </c>
-      <c r="J12" s="5">
-        <v>7</v>
-      </c>
-      <c r="K12" s="134">
-        <v>45505</v>
-      </c>
-      <c r="L12" s="134"/>
-      <c r="M12" s="134"/>
-      <c r="N12" s="134"/>
-      <c r="O12" s="134"/>
-      <c r="P12" s="134"/>
-      <c r="Q12" s="6">
-        <f>IF(J12&lt;=I12,D12*E12/12,-ROUND(CUMIPMT(E12/12,F12-I12,D12,J12-I12,J12-I12,0),2))</f>
-        <v>466.67</v>
-      </c>
-      <c r="R12" s="6">
-        <f>IF(J12&lt;=I12,0,-ROUND(CUMPRINC(E12/12,F12-I12,D12,J12-I12,J12-I12,0),2))</f>
-        <v>6455.47</v>
-      </c>
-      <c r="S12" s="6">
-        <f t="shared" si="0"/>
-        <v>6922.14</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="29" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="3">
-        <v>80000</v>
-      </c>
-      <c r="E13" s="4">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F13" s="5">
-        <v>18</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" s="5">
-        <v>1</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <v>6</v>
-      </c>
-      <c r="K13" s="134">
-        <v>45474</v>
-      </c>
-      <c r="L13" s="134">
-        <f>EDATE(G13,M13)</f>
-        <v>45383</v>
-      </c>
-      <c r="M13" s="5">
-        <v>3</v>
-      </c>
-      <c r="N13" s="135">
-        <f>D13+ROUND(CUMPRINC(E13/12,F13,D13,1,3,0),2)</f>
-        <v>67241.47</v>
-      </c>
-      <c r="O13" s="5">
-        <f>F13-M13</f>
-        <v>15</v>
-      </c>
-      <c r="P13" s="5">
-        <f>J13-M13</f>
-        <v>3</v>
-      </c>
-      <c r="Q13" s="6">
-        <f>IF(P13&lt;=I13,N13*E13/12,-ROUND(CUMIPMT(E13/12,O13-I13,N13,P13-I13,P13-I13,0),2))</f>
-        <v>341.9</v>
-      </c>
-      <c r="R13" s="6">
-        <f>IF(P13&lt;=I13,N13*E13/12,-ROUND(CUMPRINC(E13/12,O13-I13,N13,P13-I13,P13-I13,0),2))</f>
-        <v>4352.8999999999996</v>
-      </c>
-      <c r="S13" s="6">
-        <f t="shared" ref="S13" si="1">Q13+R13</f>
-        <v>4694.7999999999993</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>187</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:T2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="8" style="121" customWidth="1"/>
-    <col min="2" max="2" width="32" style="121" customWidth="1"/>
-    <col min="3" max="3" width="14" style="121" customWidth="1"/>
-    <col min="4" max="4" width="12" style="121" customWidth="1"/>
-    <col min="5" max="5" width="10" style="121" customWidth="1"/>
-    <col min="6" max="6" width="8" style="121" customWidth="1"/>
-    <col min="7" max="7" width="13" style="121" customWidth="1"/>
-    <col min="8" max="10" width="28" style="121" customWidth="1"/>
-    <col min="11" max="11" width="20" style="121" customWidth="1"/>
-    <col min="12" max="12" width="36" style="121" customWidth="1"/>
-    <col min="13" max="13" width="12" style="121" customWidth="1"/>
-    <col min="14" max="14" width="30" style="121" customWidth="1"/>
-    <col min="15" max="16384" width="8.6640625" style="121"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="137" t="s">
-        <v>45</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -3960,10 +3974,16 @@
       <c r="L1" s="137"/>
       <c r="M1" s="137"/>
       <c r="N1" s="137"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="137" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="B2" s="137"/>
       <c r="C2" s="137"/>
@@ -3978,332 +3998,925 @@
       <c r="L2" s="137"/>
       <c r="M2" s="137"/>
       <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
+    </row>
+    <row r="3" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="F4" s="5">
+        <v>12</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5">
+        <v>15</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="115">
+        <v>45337</v>
+      </c>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
+      <c r="N4" s="115"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="6">
+        <f>D4*E4/12</f>
+        <v>500</v>
+      </c>
+      <c r="R4" s="6">
+        <f>IF(J4=F4,D4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S4" s="6">
+        <f t="shared" ref="S4:S12" si="0">Q4+R4</f>
+        <v>500</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="8">
+        <v>100000</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="F5" s="10">
+        <v>12</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="10">
+        <v>15</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10">
+        <v>12</v>
+      </c>
+      <c r="K5" s="115">
+        <v>45672</v>
+      </c>
+      <c r="L5" s="115"/>
+      <c r="M5" s="115"/>
+      <c r="N5" s="115"/>
+      <c r="O5" s="115"/>
+      <c r="P5" s="115"/>
+      <c r="Q5" s="11">
+        <f>D5*E5/12</f>
+        <v>500</v>
+      </c>
+      <c r="R5" s="11">
+        <f>IF(J5=F5,D5,0)</f>
+        <v>100000</v>
+      </c>
+      <c r="S5" s="11">
+        <f t="shared" si="0"/>
+        <v>100500</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="F6" s="5">
+        <v>24</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>6</v>
+      </c>
+      <c r="K6" s="115">
+        <v>45536</v>
+      </c>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115"/>
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="6">
+        <f>D6*E6/12</f>
+        <v>375</v>
+      </c>
+      <c r="R6" s="6">
+        <f>IF(J6=F6,D6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="6">
+        <f t="shared" si="0"/>
+        <v>375</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="8">
+        <v>100000</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="F7" s="10">
+        <v>12</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="10">
+        <v>15</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>1</v>
+      </c>
+      <c r="K7" s="115">
+        <v>45337</v>
+      </c>
+      <c r="L7" s="115"/>
+      <c r="M7" s="115"/>
+      <c r="N7" s="115"/>
+      <c r="O7" s="115"/>
+      <c r="P7" s="115"/>
+      <c r="Q7" s="11">
+        <f>-CUMIPMT(E7/12,F7,D7,J7,J7,0)</f>
+        <v>500</v>
+      </c>
+      <c r="R7" s="11">
+        <f>-CUMPRINC(E7/12,F7,D7,J7,J7,0)</f>
+        <v>8106.6429707080642</v>
+      </c>
+      <c r="S7" s="11">
+        <f t="shared" si="0"/>
+        <v>8606.6429707080642</v>
+      </c>
+      <c r="T7" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="F8" s="5">
+        <v>12</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="5">
+        <v>15</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>6</v>
+      </c>
+      <c r="K8" s="115">
+        <v>45488</v>
+      </c>
+      <c r="L8" s="115"/>
+      <c r="M8" s="115"/>
+      <c r="N8" s="115"/>
+      <c r="O8" s="115"/>
+      <c r="P8" s="115"/>
+      <c r="Q8" s="6">
+        <f>-CUMIPMT(E8/12,F8,D8,J8,J8,0)</f>
+        <v>295.29710632731621</v>
+      </c>
+      <c r="R8" s="6">
+        <f>-CUMPRINC(E8/12,F8,D8,J8,J8,0)</f>
+        <v>8311.345864380748</v>
+      </c>
+      <c r="S8" s="6">
+        <f t="shared" si="0"/>
+        <v>8606.6429707080642</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="8">
+        <v>100000</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="F9" s="10">
+        <v>12</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="10">
+        <v>15</v>
+      </c>
+      <c r="I9" s="10">
+        <v>0</v>
+      </c>
+      <c r="J9" s="10">
+        <v>12</v>
+      </c>
+      <c r="K9" s="115">
+        <v>45672</v>
+      </c>
+      <c r="L9" s="115"/>
+      <c r="M9" s="115"/>
+      <c r="N9" s="115"/>
+      <c r="O9" s="115"/>
+      <c r="P9" s="115"/>
+      <c r="Q9" s="11">
+        <f>-CUMIPMT(E9/12,F9,D9,J9,J9,0)</f>
+        <v>42.819119257253988</v>
+      </c>
+      <c r="R9" s="11">
+        <f>-CUMPRINC(E9/12,F9,D9,J9,J9,0)</f>
+        <v>8563.8238514508103</v>
+      </c>
+      <c r="S9" s="11">
+        <f t="shared" si="0"/>
+        <v>8606.6429707080642</v>
+      </c>
+      <c r="T9" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="F10" s="5">
+        <v>24</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>1</v>
+      </c>
+      <c r="K10" s="115">
+        <v>45474</v>
+      </c>
+      <c r="L10" s="115"/>
+      <c r="M10" s="115"/>
+      <c r="N10" s="115"/>
+      <c r="O10" s="115"/>
+      <c r="P10" s="115"/>
+      <c r="Q10" s="6">
+        <f>-CUMIPMT(E10/12,F10,D10,J10,J10,0)</f>
+        <v>400.00000000000045</v>
+      </c>
+      <c r="R10" s="6">
+        <f>-CUMPRINC(E10/12,F10,D10,J10,J10,0)</f>
+        <v>2313.6374873710488</v>
+      </c>
+      <c r="S10" s="6">
+        <f t="shared" si="0"/>
+        <v>2713.6374873710492</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E11" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>18</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="10">
+        <v>1</v>
+      </c>
+      <c r="I11" s="10">
+        <v>6</v>
+      </c>
+      <c r="J11" s="10">
+        <v>1</v>
+      </c>
+      <c r="K11" s="115">
+        <v>45323</v>
+      </c>
+      <c r="L11" s="115"/>
+      <c r="M11" s="115"/>
+      <c r="N11" s="115"/>
+      <c r="O11" s="115"/>
+      <c r="P11" s="115"/>
+      <c r="Q11" s="6">
+        <f>IF(J11&lt;=I11,D11*E11/12,-ROUND(CUMIPMT(E11/12,F11-I11,D11,J11-I11,J11-I11,0),2))</f>
+        <v>466.66666666666674</v>
+      </c>
+      <c r="R11" s="6">
+        <f>IF(J11&lt;=I11,0,-ROUND(CUMPRINC(E11/12,F11-I11,D11,J11-I11,J11-I11,0),2))</f>
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <f t="shared" si="0"/>
+        <v>466.66666666666674</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E12" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F12" s="5">
+        <v>18</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
+        <v>6</v>
+      </c>
+      <c r="J12" s="5">
+        <v>7</v>
+      </c>
+      <c r="K12" s="115">
+        <v>45505</v>
+      </c>
+      <c r="L12" s="115"/>
+      <c r="M12" s="115"/>
+      <c r="N12" s="115"/>
+      <c r="O12" s="115"/>
+      <c r="P12" s="115"/>
+      <c r="Q12" s="6">
+        <f>IF(J12&lt;=I12,D12*E12/12,-ROUND(CUMIPMT(E12/12,F12-I12,D12,J12-I12,J12-I12,0),2))</f>
+        <v>466.67</v>
+      </c>
+      <c r="R12" s="6">
+        <f>IF(J12&lt;=I12,0,-ROUND(CUMPRINC(E12/12,F12-I12,D12,J12-I12,J12-I12,0),2))</f>
+        <v>6455.47</v>
+      </c>
+      <c r="S12" s="6">
+        <f t="shared" si="0"/>
+        <v>6922.14</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8" style="103" customWidth="1"/>
+    <col min="2" max="2" width="32" style="103" customWidth="1"/>
+    <col min="3" max="3" width="14" style="103" customWidth="1"/>
+    <col min="4" max="4" width="12" style="103" customWidth="1"/>
+    <col min="5" max="5" width="10" style="103" customWidth="1"/>
+    <col min="6" max="6" width="8" style="103" customWidth="1"/>
+    <col min="7" max="7" width="13" style="103" customWidth="1"/>
+    <col min="8" max="10" width="28" style="103" customWidth="1"/>
+    <col min="11" max="11" width="20" style="103" customWidth="1"/>
+    <col min="12" max="12" width="36" style="103" customWidth="1"/>
+    <col min="13" max="13" width="12" style="103" customWidth="1"/>
+    <col min="14" max="14" width="30" style="103" customWidth="1"/>
+    <col min="15" max="16384" width="8.6640625" style="103"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="138" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="138"/>
+      <c r="M1" s="138"/>
+      <c r="N1" s="138"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="138" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="122" t="s">
+      <c r="A3" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="122" t="s">
+      <c r="B3" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="122" t="s">
+      <c r="C3" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="122" t="s">
+      <c r="D3" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="122" t="s">
+      <c r="E3" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="122" t="s">
+      <c r="F3" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="122" t="s">
+      <c r="G3" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="122" t="s">
+      <c r="H3" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="122" t="s">
-        <v>291</v>
-      </c>
-      <c r="J3" s="122" t="s">
-        <v>293</v>
-      </c>
-      <c r="K3" s="122" t="s">
+      <c r="I3" s="104" t="s">
+        <v>282</v>
+      </c>
+      <c r="J3" s="104" t="s">
+        <v>283</v>
+      </c>
+      <c r="K3" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="122" t="s">
+      <c r="L3" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="122" t="s">
+      <c r="M3" s="104" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="122" t="s">
+      <c r="N3" s="104" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="123" t="s">
+      <c r="A4" s="105" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="123" t="s">
+      <c r="C4" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="124">
+      <c r="D4" s="106">
         <v>100000</v>
       </c>
-      <c r="E4" s="125">
+      <c r="E4" s="107">
         <v>0.06</v>
       </c>
-      <c r="F4" s="126">
+      <c r="F4" s="108">
         <v>12</v>
       </c>
-      <c r="G4" s="126" t="s">
+      <c r="G4" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="123" t="s">
+      <c r="H4" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="123"/>
-      <c r="J4" s="123"/>
-      <c r="K4" s="127">
+      <c r="I4" s="105"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="109">
         <f>D4</f>
         <v>100000</v>
       </c>
-      <c r="L4" s="123" t="s">
+      <c r="L4" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="M4" s="124">
+      <c r="M4" s="106">
         <v>0.01</v>
       </c>
-      <c r="N4" s="123"/>
+      <c r="N4" s="105"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="110" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="128" t="s">
+      <c r="B5" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="128" t="s">
+      <c r="C5" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="129">
+      <c r="D5" s="111">
         <v>100000</v>
       </c>
-      <c r="E5" s="130">
+      <c r="E5" s="112">
         <v>0.06</v>
       </c>
-      <c r="F5" s="131">
+      <c r="F5" s="113">
         <v>12</v>
       </c>
-      <c r="G5" s="131" t="s">
+      <c r="G5" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="128" t="s">
+      <c r="H5" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="132">
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="114">
         <f>D5-20000</f>
         <v>80000</v>
       </c>
-      <c r="L5" s="128" t="s">
+      <c r="L5" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="M5" s="129">
+      <c r="M5" s="111">
         <v>0.01</v>
       </c>
-      <c r="N5" s="128"/>
+      <c r="N5" s="110"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="123" t="s">
+      <c r="B6" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="123" t="s">
+      <c r="C6" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="124">
+      <c r="D6" s="106">
         <v>100000</v>
       </c>
-      <c r="E6" s="125">
+      <c r="E6" s="107">
         <v>0.06</v>
       </c>
-      <c r="F6" s="126">
+      <c r="F6" s="108">
         <v>12</v>
       </c>
-      <c r="G6" s="126" t="s">
+      <c r="G6" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="123" t="s">
+      <c r="H6" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="123"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="127">
+      <c r="I6" s="105"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="109">
         <f>D6-20000-10000</f>
         <v>70000</v>
       </c>
-      <c r="L6" s="123" t="s">
+      <c r="L6" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="M6" s="124">
+      <c r="M6" s="106">
         <v>0.01</v>
       </c>
-      <c r="N6" s="123"/>
+      <c r="N6" s="105"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="128" t="s">
+      <c r="A7" s="110" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="128" t="s">
+      <c r="B7" s="110" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="128" t="s">
+      <c r="C7" s="110" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="129">
+      <c r="D7" s="111">
         <v>100000</v>
       </c>
-      <c r="E7" s="130">
+      <c r="E7" s="112">
         <v>0.06</v>
       </c>
-      <c r="F7" s="131">
+      <c r="F7" s="113">
         <v>12</v>
       </c>
-      <c r="G7" s="131" t="s">
+      <c r="G7" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="128" t="s">
+      <c r="H7" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="128"/>
-      <c r="J7" s="128"/>
-      <c r="K7" s="132">
+      <c r="I7" s="110"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="114">
         <f>D7</f>
         <v>100000</v>
       </c>
-      <c r="L7" s="128" t="s">
+      <c r="L7" s="110" t="s">
         <v>66</v>
       </c>
-      <c r="M7" s="129">
+      <c r="M7" s="111">
         <v>0.01</v>
       </c>
-      <c r="N7" s="128"/>
+      <c r="N7" s="110"/>
     </row>
     <row r="8" spans="1:14" ht="28" x14ac:dyDescent="0.2">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="123" t="s">
+      <c r="B8" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="123" t="s">
+      <c r="C8" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="124">
+      <c r="D8" s="106">
         <v>100000</v>
       </c>
-      <c r="E8" s="125">
+      <c r="E8" s="107">
         <v>0.06</v>
       </c>
-      <c r="F8" s="126">
+      <c r="F8" s="108">
         <v>12</v>
       </c>
-      <c r="G8" s="126" t="s">
+      <c r="G8" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="123" t="s">
+      <c r="H8" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="I8" s="123"/>
-      <c r="J8" s="123"/>
-      <c r="K8" s="127">
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
+      <c r="K8" s="109">
         <f>D8+ROUND(CUMPRINC(E8/12,F8,D8,1,3,0),2)</f>
         <v>75558.27</v>
       </c>
-      <c r="L8" s="123" t="s">
+      <c r="L8" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="124">
+      <c r="M8" s="106">
         <v>0.1</v>
       </c>
-      <c r="N8" s="123" t="s">
+      <c r="N8" s="105" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="128" t="s">
+      <c r="A9" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="128" t="s">
+      <c r="B9" s="110" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="128" t="s">
+      <c r="C9" s="110" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="129">
+      <c r="D9" s="111">
         <v>100000</v>
       </c>
-      <c r="E9" s="130">
+      <c r="E9" s="112">
         <v>0.06</v>
       </c>
-      <c r="F9" s="131">
+      <c r="F9" s="113">
         <v>12</v>
       </c>
-      <c r="G9" s="131" t="s">
+      <c r="G9" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="128" t="s">
+      <c r="H9" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="128"/>
-      <c r="J9" s="128"/>
-      <c r="K9" s="132">
+      <c r="I9" s="110"/>
+      <c r="J9" s="110"/>
+      <c r="K9" s="114">
         <f>D9+ROUND(CUMPRINC(E9/12,F9,D9,1,12,0),2)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="128" t="s">
+      <c r="L9" s="110" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="129">
+      <c r="M9" s="111">
         <v>0.1</v>
       </c>
-      <c r="N9" s="128"/>
-    </row>
-    <row r="10" spans="1:14" ht="28" x14ac:dyDescent="0.2">
-      <c r="A10" s="123" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="123" t="s">
-        <v>292</v>
-      </c>
-      <c r="C10" s="123" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="124">
-        <v>100000</v>
-      </c>
-      <c r="E10" s="125">
-        <v>0.06</v>
-      </c>
-      <c r="F10" s="126">
-        <v>12</v>
-      </c>
-      <c r="G10" s="126" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="123" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="127">
-        <f>D10+CUMPRINC(E10/12,F10,D10-30000,1,3,0)-30000</f>
-        <v>52890.788144068647</v>
-      </c>
-      <c r="J10" s="133">
-        <v>9</v>
-      </c>
-      <c r="K10" s="127">
-        <f>I10-30000+ROUND(CUMPRINC(E10/12,J10,I10-30000,1,3,0),2)</f>
-        <v>15374.408144068646</v>
-      </c>
-      <c r="L10" s="123" t="s">
-        <v>78</v>
-      </c>
-      <c r="M10" s="124">
-        <v>1</v>
-      </c>
-      <c r="N10" s="123" t="s">
-        <v>79</v>
-      </c>
+      <c r="N9" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4334,34 +4947,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="136" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
+      <c r="A1" s="137" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="136" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
+      <c r="A2" s="137" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -4386,13 +4999,13 @@
         <v>8</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>16</v>
@@ -4400,10 +5013,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
@@ -4421,24 +5034,24 @@
         <v>41</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>54</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>19</v>
@@ -4456,24 +5069,24 @@
         <v>41</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>54</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>19</v>
@@ -4488,27 +5101,27 @@
         <v>12</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>54</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>19</v>
@@ -4526,24 +5139,24 @@
         <v>20</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>19</v>
@@ -4558,27 +5171,27 @@
         <v>24</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>54</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>19</v>
@@ -4596,16 +5209,16 @@
         <v>20</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -4619,13 +5232,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S82"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:S80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="24.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" style="19"/>
     <col min="2" max="2" width="42" style="19" customWidth="1"/>
-    <col min="3" max="3" width="23.1640625" style="109" customWidth="1"/>
+    <col min="3" max="3" width="23.1640625" style="99" customWidth="1"/>
     <col min="4" max="4" width="24.5" style="19"/>
     <col min="5" max="5" width="20.6640625" style="19" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" style="19" customWidth="1"/>
@@ -4646,31 +5259,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
+      <c r="A1" s="139" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
-      <c r="C2" s="104"/>
+      <c r="C2" s="94"/>
       <c r="D2" s="18"/>
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
     </row>
     <row r="3" spans="1:18" s="22" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B3" s="35">
         <v>46101</v>
       </c>
-      <c r="C3" s="105"/>
+      <c r="C3" s="95"/>
       <c r="D3" s="37"/>
       <c r="E3" s="37"/>
       <c r="F3" s="37"/>
@@ -4678,7 +5291,7 @@
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
-      <c r="C4" s="104"/>
+      <c r="C4" s="94"/>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
@@ -4692,7 +5305,7 @@
         <f>COLUMN()</f>
         <v>2</v>
       </c>
-      <c r="C5" s="104">
+      <c r="C5" s="94">
         <f>COLUMN()</f>
         <v>3</v>
       </c>
@@ -4754,74 +5367,74 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="81" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="106"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="81"/>
-      <c r="P6" s="81"/>
-      <c r="Q6" s="81"/>
+      <c r="A6" s="80" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="80"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="80"/>
     </row>
     <row r="7" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J7" s="36" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K7" s="36" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L7" s="36" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="M7" s="36" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="N7" s="36" t="s">
-        <v>254</v>
-      </c>
-      <c r="O7" s="111" t="s">
-        <v>265</v>
+        <v>247</v>
+      </c>
+      <c r="O7" s="101" t="s">
+        <v>258</v>
       </c>
       <c r="P7" s="36" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="Q7" s="36" t="s">
         <v>7</v>
@@ -4829,10 +5442,10 @@
     </row>
     <row r="8" spans="1:18" s="22" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="42" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C8" s="38">
         <v>100000</v>
@@ -4846,7 +5459,7 @@
       <c r="F8" s="44">
         <v>0.06</v>
       </c>
-      <c r="G8" s="117">
+      <c r="G8" s="102">
         <v>36</v>
       </c>
       <c r="H8" s="44">
@@ -4856,18 +5469,18 @@
         <f>IF($B$3-T_Prestamos[[#This Row],[Fecha inicio]]&lt;=365,H8*T_Prestamos[[#This Row],[Principal]],0)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="83">
         <v>200000</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="84">
         <f>C8/J8</f>
         <v>0.5</v>
       </c>
       <c r="L8" s="39" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="M8" s="40"/>
-      <c r="N8" s="82">
+      <c r="N8" s="81">
         <f>IF(T_Prestamos[[#This Row],[Estado final]]="Cancelado",0,SUMIFS(T_Acciones_Prestamos[Saldo Principal],T_Acciones_Prestamos[Préstamo],T_Prestamos[[#This Row],[Ref]],T_Acciones_Prestamos[Orden],_xlfn.MAXIFS(T_Acciones_Prestamos[Orden],T_Acciones_Prestamos[Préstamo],T_Prestamos[[#This Row],[Ref]])))</f>
         <v>0</v>
       </c>
@@ -4875,7 +5488,7 @@
         <f>DATEDIF(T_Prestamos[[#This Row],[Fecha inicio]],DATE(YEAR($B$3),1,DAY(T_Prestamos[[#This Row],[Fecha inicio]])),"m")</f>
         <v>19</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="81">
         <f>IF(T_Prestamos[[#This Row],[Estado final]]="Cancelado",0,IF(T_Prestamos[[#This Row],[Tipo cálculo]]="Americano",T_Prestamos[[#This Row],[Principal final]]*T_Prestamos[[#This Row],[% interés]],-CUMIPMT(T_Prestamos[[#This Row],[% interés]]/12,T_Prestamos[[#This Row],[Duración - meses]],T_Prestamos[[#This Row],[Principal]],T_Prestamos[[#This Row],[Cuota 1 año curso]],MIN(T_Prestamos[[#This Row],[Cuota 1 año curso]]+11,T_Prestamos[[#This Row],[Duración - meses]]),0)))</f>
         <v>0</v>
       </c>
@@ -4886,10 +5499,10 @@
     </row>
     <row r="9" spans="1:18" s="22" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="42" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C9" s="38">
         <v>60000</v>
@@ -4903,7 +5516,7 @@
       <c r="F9" s="46">
         <v>0.08</v>
       </c>
-      <c r="G9" s="117">
+      <c r="G9" s="102">
         <v>48</v>
       </c>
       <c r="H9" s="44">
@@ -4913,28 +5526,28 @@
         <f>IF($B$3-T_Prestamos[[#This Row],[Fecha inicio]]&lt;=365,H9*T_Prestamos[[#This Row],[Principal]],0)</f>
         <v>1200</v>
       </c>
-      <c r="J9" s="84">
+      <c r="J9" s="83">
         <v>200000</v>
       </c>
-      <c r="K9" s="85">
+      <c r="K9" s="84">
         <f>C9/J9</f>
         <v>0.3</v>
       </c>
       <c r="L9" s="39" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="M9" s="39" t="s">
-        <v>238</v>
-      </c>
-      <c r="N9" s="82">
+        <v>234</v>
+      </c>
+      <c r="N9" s="81">
         <f>IF(T_Prestamos[[#This Row],[Estado final]]="Cancelado",0,SUMIFS(T_Acciones_Prestamos[Saldo Principal],T_Acciones_Prestamos[Préstamo],T_Prestamos[[#This Row],[Ref]],T_Acciones_Prestamos[Orden],_xlfn.MAXIFS(T_Acciones_Prestamos[Orden],T_Acciones_Prestamos[Préstamo],T_Prestamos[[#This Row],[Ref]])))</f>
-        <v>38508.32</v>
+        <v>56784.33</v>
       </c>
       <c r="O9" s="22">
         <f>DATEDIF(T_Prestamos[[#This Row],[Fecha inicio]],DATE(YEAR($B$3),1,DAY(T_Prestamos[[#This Row],[Fecha inicio]])),"m")</f>
         <v>5</v>
       </c>
-      <c r="P9" s="82">
+      <c r="P9" s="81">
         <f>IF(T_Prestamos[[#This Row],[Estado final]]="Cancelado",0,IF(T_Prestamos[[#This Row],[Tipo cálculo]]="Americano",T_Prestamos[[#This Row],[Principal final]]*T_Prestamos[[#This Row],[% interés]],-CUMIPMT(T_Prestamos[[#This Row],[% interés]]/12,T_Prestamos[[#This Row],[Duración - meses]],T_Prestamos[[#This Row],[Principal]],T_Prestamos[[#This Row],[Cuota 1 año curso]],MIN(T_Prestamos[[#This Row],[Cuota 1 año curso]]+11,T_Prestamos[[#This Row],[Duración - meses]]),0)))</f>
         <v>3963.8757846049866</v>
       </c>
@@ -4945,10 +5558,10 @@
     </row>
     <row r="10" spans="1:18" s="22" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="42" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C10" s="38">
         <v>80000</v>
@@ -4962,7 +5575,7 @@
       <c r="F10" s="44">
         <v>0.09</v>
       </c>
-      <c r="G10" s="117">
+      <c r="G10" s="102">
         <v>60</v>
       </c>
       <c r="H10" s="44">
@@ -4972,23 +5585,23 @@
         <f>IF($B$3-T_Prestamos[[#This Row],[Fecha inicio]]&lt;=365,H10*T_Prestamos[[#This Row],[Principal]],0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="84">
+      <c r="J10" s="83">
         <v>300000</v>
       </c>
-      <c r="K10" s="85">
+      <c r="K10" s="84">
         <f>C10/J10</f>
         <v>0.26666666666666666</v>
       </c>
       <c r="L10" s="39" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="M10" s="40"/>
-      <c r="N10" s="82"/>
+      <c r="N10" s="81"/>
       <c r="O10" s="22">
         <f>DATEDIF(T_Prestamos[[#This Row],[Fecha inicio]],DATE(YEAR($B$3),1,DAY(T_Prestamos[[#This Row],[Fecha inicio]])),"m")</f>
         <v>16</v>
       </c>
-      <c r="P10" s="82">
+      <c r="P10" s="81">
         <f>IF(T_Prestamos[[#This Row],[Estado final]]="Cancelado",0,IF(T_Prestamos[[#This Row],[Tipo cálculo]]="Americano",T_Prestamos[[#This Row],[Principal final]]*T_Prestamos[[#This Row],[% interés]],-CUMIPMT(T_Prestamos[[#This Row],[% interés]]/12,T_Prestamos[[#This Row],[Duración - meses]],T_Prestamos[[#This Row],[Principal]],T_Prestamos[[#This Row],[Cuota 1 año curso]],MIN(T_Prestamos[[#This Row],[Cuota 1 año curso]]+11,T_Prestamos[[#This Row],[Duración - meses]]),0)))</f>
         <v>0</v>
       </c>
@@ -4999,595 +5612,594 @@
     </row>
     <row r="11" spans="1:18" s="22" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="42" t="s">
-        <v>288</v>
+        <v>221</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="C11" s="82">
-        <f>SUMIFS(T_Acciones_Prestamos[Saldo Principal],T_Acciones_Prestamos[Préstamo],A10,T_Acciones_Prestamos[Orden],_xlfn.MAXIFS(T_Acciones_Prestamos[Orden],T_Acciones_Prestamos[Préstamo],A10))</f>
-        <v>30000</v>
-      </c>
-      <c r="D11" s="60">
-        <f>G27</f>
-        <v>45782</v>
-      </c>
-      <c r="E11" s="115" t="str">
-        <f>E10</f>
-        <v>Americano</v>
-      </c>
-      <c r="F11" s="116">
-        <f>F10</f>
-        <v>0.09</v>
-      </c>
-      <c r="G11" s="118">
-        <f>G10-E27</f>
-        <v>52</v>
+        <v>281</v>
+      </c>
+      <c r="C11" s="38">
+        <v>80000</v>
+      </c>
+      <c r="D11" s="43">
+        <v>45575</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="44">
+        <v>0.08</v>
+      </c>
+      <c r="G11" s="102">
+        <v>36</v>
       </c>
       <c r="H11" s="44">
-        <v>0</v>
-      </c>
-      <c r="I11" s="112">
+        <v>0.01</v>
+      </c>
+      <c r="I11" s="45">
         <f>IF($B$3-T_Prestamos[[#This Row],[Fecha inicio]]&lt;=365,H11*T_Prestamos[[#This Row],[Principal]],0)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="119">
-        <f>J10</f>
-        <v>300000</v>
-      </c>
-      <c r="K11" s="120">
-        <f>K10</f>
-        <v>0.26666666666666666</v>
+      <c r="J11" s="83">
+        <v>250000</v>
+      </c>
+      <c r="K11" s="84">
+        <f>C11/J11</f>
+        <v>0.32</v>
       </c>
       <c r="L11" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="M11" s="39"/>
-      <c r="N11" s="82">
-        <f>IF(T_Prestamos[[#This Row],[Estado final]]="Cancelado",0,SUMIFS(T_Acciones_Prestamos[Saldo Principal],T_Acciones_Prestamos[Préstamo],T_Prestamos[[#This Row],[Ref]],T_Acciones_Prestamos[Orden],_xlfn.MAXIFS(T_Acciones_Prestamos[Orden],T_Acciones_Prestamos[Préstamo],T_Prestamos[[#This Row],[Ref]])))</f>
-        <v>30000</v>
-      </c>
-      <c r="O11" s="113">
-        <f>DATEDIF(T_Prestamos[[#This Row],[Fecha inicio]],DATE(YEAR($B$3),1,DAY(T_Prestamos[[#This Row],[Fecha inicio]])),"m")</f>
-        <v>8</v>
-      </c>
-      <c r="P11" s="82">
-        <f>IF(T_Prestamos[[#This Row],[Estado final]]="Cancelado",0,IF(T_Prestamos[[#This Row],[Tipo cálculo]]="Americano",T_Prestamos[[#This Row],[Principal final]]*T_Prestamos[[#This Row],[% interés]],-CUMIPMT(T_Prestamos[[#This Row],[% interés]]/12,T_Prestamos[[#This Row],[Duración - meses]],T_Prestamos[[#This Row],[Principal]],T_Prestamos[[#This Row],[Cuota 1 año curso]],MIN(T_Prestamos[[#This Row],[Cuota 1 año curso]]+11,T_Prestamos[[#This Row],[Duración - meses]]),0)))</f>
-        <v>2700</v>
-      </c>
-      <c r="Q11" s="114">
-        <f>DATEDIF(T_Prestamos[[#This Row],[Fecha inicio]],$B$3,"m")</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" s="22" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="C12" s="38">
-        <v>80000</v>
-      </c>
-      <c r="D12" s="43">
-        <v>45575</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="44">
-        <v>0.08</v>
-      </c>
-      <c r="G12" s="117">
-        <v>36</v>
-      </c>
-      <c r="H12" s="44">
-        <v>0.01</v>
-      </c>
-      <c r="I12" s="45">
-        <f>IF($B$3-T_Prestamos[[#This Row],[Fecha inicio]]&lt;=365,H12*T_Prestamos[[#This Row],[Principal]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="84">
-        <v>250000</v>
-      </c>
-      <c r="K12" s="85">
-        <f>C12/J12</f>
-        <v>0.32</v>
-      </c>
-      <c r="L12" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="M12" s="39" t="s">
-        <v>246</v>
-      </c>
-      <c r="N12" s="82">
+        <v>189</v>
+      </c>
+      <c r="M11" s="40"/>
+      <c r="N11" s="81">
         <f>IF(T_Prestamos[[#This Row],[Estado final]]="Cancelado",0,SUMIFS(T_Acciones_Prestamos[Saldo Principal],T_Acciones_Prestamos[Préstamo],T_Prestamos[[#This Row],[Ref]],T_Acciones_Prestamos[Orden],_xlfn.MAXIFS(T_Acciones_Prestamos[Orden],T_Acciones_Prestamos[Préstamo],T_Prestamos[[#This Row],[Ref]])))</f>
         <v>74039.710000000006</v>
       </c>
-      <c r="O12" s="22">
+      <c r="O11" s="22">
         <f>DATEDIF(T_Prestamos[[#This Row],[Fecha inicio]],DATE(YEAR($B$3),1,DAY(T_Prestamos[[#This Row],[Fecha inicio]])),"m")</f>
         <v>15</v>
       </c>
-      <c r="P12" s="82">
+      <c r="P11" s="81">
         <f>IF(T_Prestamos[[#This Row],[Estado final]]="Cancelado",0,IF(T_Prestamos[[#This Row],[Tipo cálculo]]="Americano",T_Prestamos[[#This Row],[Principal final]]*T_Prestamos[[#This Row],[% interés]],-CUMIPMT(T_Prestamos[[#This Row],[% interés]]/12,T_Prestamos[[#This Row],[Duración - meses]],T_Prestamos[[#This Row],[Principal]],T_Prestamos[[#This Row],[Cuota 1 año curso]],MIN(T_Prestamos[[#This Row],[Cuota 1 año curso]]+11,T_Prestamos[[#This Row],[Duración - meses]]),0)))</f>
         <v>3116.680486291847</v>
       </c>
-      <c r="Q12" s="19">
+      <c r="Q11" s="19">
         <f>DATEDIF(T_Prestamos[[#This Row],[Fecha inicio]],$B$3,"m")</f>
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="80" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="71"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="73"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="79"/>
-      <c r="N13" s="79"/>
-    </row>
-    <row r="14" spans="1:18" s="34" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="33"/>
-      <c r="N14" s="32"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="81" t="s">
+    <row r="12" spans="1:18" s="79" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="70"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="76"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="78"/>
+      <c r="N12" s="78"/>
+    </row>
+    <row r="13" spans="1:18" s="34" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="33"/>
+      <c r="N13" s="32"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A14" s="80" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="80"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="80"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="80"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="80"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="80"/>
+      <c r="R14" s="80"/>
+    </row>
+    <row r="15" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="F15" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B15" s="81"/>
-      <c r="C15" s="106"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="81"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="81"/>
-      <c r="P15" s="81"/>
-      <c r="Q15" s="81"/>
-      <c r="R15" s="81"/>
+      <c r="G15" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="M15" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="N15" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="O15" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="P15" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q15" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="R15" s="20" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="16" spans="1:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="H16" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="I16" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="J16" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="K16" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="L16" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="M16" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="N16" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="O16" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="P16" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q16" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="R16" s="20" t="s">
-        <v>7</v>
+      <c r="B16" s="58" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" s="46">
+        <v>0.4</v>
+      </c>
+      <c r="E16" s="48">
+        <f>L16*D16</f>
+        <v>40000</v>
+      </c>
+      <c r="F16" s="46">
+        <v>0.02</v>
+      </c>
+      <c r="G16" s="48">
+        <f>T_CCP[[#This Row],[Ingr. Anuales prest.]]*T_CCP[[#This Row],[% participación]]</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="48">
+        <f>T_CCP[[#This Row],[Participado final]]*T_CCP[[#This Row],[% gestión]]</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="48">
+        <f>T_CCP[[#This Row],[Garantías prestamo]]*T_CCP[[#This Row],[% participación]]</f>
+        <v>80000</v>
+      </c>
+      <c r="J16" s="48">
+        <f>T_CCP[[#This Row],[Principal final]]*T_CCP[[#This Row],[% participación]]</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="49">
+        <f>VLOOKUP(C16,$A$8:$L$11,$F$5,FALSE)</f>
+        <v>0.06</v>
+      </c>
+      <c r="L16" s="50">
+        <f>VLOOKUP(C16,$A$8:$L$11,$C$5,FALSE)</f>
+        <v>100000</v>
+      </c>
+      <c r="M16" s="50" t="str">
+        <f>IF(VLOOKUP(C16,T_Prestamos[],$L$5,FALSE)=0,"",VLOOKUP(C16,T_Prestamos[],$L$5,FALSE))</f>
+        <v>Cancelado</v>
+      </c>
+      <c r="N16" s="50" t="str">
+        <f>IF(VLOOKUP(C16,T_Prestamos[],$M$5,FALSE)=0,"",VLOOKUP(C16,T_Prestamos[],$M$5,FALSE))</f>
+        <v/>
+      </c>
+      <c r="O16" s="50">
+        <f>VLOOKUP(C16,T_Prestamos[],$N$5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="50">
+        <f>VLOOKUP(C16,T_Prestamos[],$P$5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="88">
+        <f>VLOOKUP(C16,T_Prestamos[],$J$5,FALSE)</f>
+        <v>200000</v>
+      </c>
+      <c r="R16" s="89">
+        <f>VLOOKUP(C16,T_Prestamos[],$Q$5,FALSE)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="59" t="s">
-        <v>118</v>
+        <v>115</v>
+      </c>
+      <c r="B17" s="58" t="s">
+        <v>116</v>
       </c>
       <c r="C17" s="47" t="s">
         <v>210</v>
       </c>
       <c r="D17" s="46">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="48">
         <f>L17*D17</f>
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="F17" s="46">
         <v>0.02</v>
       </c>
       <c r="G17" s="48">
         <f>T_CCP[[#This Row],[Ingr. Anuales prest.]]*T_CCP[[#This Row],[% participación]]</f>
-        <v>0</v>
+        <v>1981.9378923024933</v>
       </c>
       <c r="H17" s="48">
-        <f>IF(T_CCP[[#This Row],[Estado final]]="Activo",E17*F17,0)</f>
-        <v>0</v>
+        <f>T_CCP[[#This Row],[Participado final]]*T_CCP[[#This Row],[% gestión]]</f>
+        <v>567.8433</v>
       </c>
       <c r="I17" s="48">
         <f>T_CCP[[#This Row],[Garantías prestamo]]*T_CCP[[#This Row],[% participación]]</f>
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="J17" s="48">
         <f>T_CCP[[#This Row],[Principal final]]*T_CCP[[#This Row],[% participación]]</f>
-        <v>0</v>
+        <v>28392.165000000001</v>
       </c>
       <c r="K17" s="49">
-        <f>VLOOKUP(C17,$A$8:$L$12,$F$5,FALSE)</f>
-        <v>0.06</v>
+        <f>VLOOKUP(C17,$A$8:$L$11,$F$5,FALSE)</f>
+        <v>0.08</v>
       </c>
       <c r="L17" s="50">
-        <f>VLOOKUP(C17,$A$8:$L$12,$C$5,FALSE)</f>
-        <v>100000</v>
+        <f>VLOOKUP(C17,$A$8:$L$11,$C$5,FALSE)</f>
+        <v>60000</v>
       </c>
       <c r="M17" s="50" t="str">
         <f>IF(VLOOKUP(C17,T_Prestamos[],$L$5,FALSE)=0,"",VLOOKUP(C17,T_Prestamos[],$L$5,FALSE))</f>
-        <v>Cancelado</v>
+        <v>Activo</v>
       </c>
       <c r="N17" s="50" t="str">
         <f>IF(VLOOKUP(C17,T_Prestamos[],$M$5,FALSE)=0,"",VLOOKUP(C17,T_Prestamos[],$M$5,FALSE))</f>
-        <v/>
+        <v>Al día</v>
       </c>
       <c r="O17" s="50">
         <f>VLOOKUP(C17,T_Prestamos[],$N$5,FALSE)</f>
-        <v>0</v>
+        <v>56784.33</v>
       </c>
       <c r="P17" s="50">
         <f>VLOOKUP(C17,T_Prestamos[],$P$5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="89">
+        <v>3963.8757846049866</v>
+      </c>
+      <c r="Q17" s="88">
         <f>VLOOKUP(C17,T_Prestamos[],$J$5,FALSE)</f>
         <v>200000</v>
       </c>
-      <c r="R17" s="90">
+      <c r="R17" s="89">
         <f>VLOOKUP(C17,T_Prestamos[],$Q$5,FALSE)</f>
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="B18" s="59" t="s">
-        <v>120</v>
+        <v>117</v>
+      </c>
+      <c r="B18" s="58" t="s">
+        <v>118</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>214</v>
+        <v>140</v>
       </c>
       <c r="D18" s="46">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E18" s="48">
         <f>L18*D18</f>
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="F18" s="46">
         <v>0.02</v>
       </c>
       <c r="G18" s="48">
         <f>T_CCP[[#This Row],[Ingr. Anuales prest.]]*T_CCP[[#This Row],[% participación]]</f>
-        <v>1981.9378923024933</v>
+        <v>0</v>
       </c>
       <c r="H18" s="48">
-        <f>IF(T_CCP[[#This Row],[Estado final]]="Activo",E18*F18,0)</f>
-        <v>600</v>
+        <f>T_CCP[[#This Row],[Participado final]]*T_CCP[[#This Row],[% gestión]]</f>
+        <v>0</v>
       </c>
       <c r="I18" s="48">
         <f>T_CCP[[#This Row],[Garantías prestamo]]*T_CCP[[#This Row],[% participación]]</f>
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="J18" s="48">
         <f>T_CCP[[#This Row],[Principal final]]*T_CCP[[#This Row],[% participación]]</f>
-        <v>19254.16</v>
+        <v>0</v>
       </c>
       <c r="K18" s="49">
-        <f>VLOOKUP(C18,$A$8:$L$12,$F$5,FALSE)</f>
-        <v>0.08</v>
+        <f>VLOOKUP(C18,$A$8:$L$11,$F$5,FALSE)</f>
+        <v>0.09</v>
       </c>
       <c r="L18" s="50">
-        <f>VLOOKUP(C18,$A$8:$L$12,$C$5,FALSE)</f>
-        <v>60000</v>
+        <f>VLOOKUP(C18,$A$8:$L$11,$C$5,FALSE)</f>
+        <v>80000</v>
       </c>
       <c r="M18" s="50" t="str">
         <f>IF(VLOOKUP(C18,T_Prestamos[],$L$5,FALSE)=0,"",VLOOKUP(C18,T_Prestamos[],$L$5,FALSE))</f>
-        <v>Activo</v>
+        <v>Cancelado</v>
       </c>
       <c r="N18" s="50" t="str">
         <f>IF(VLOOKUP(C18,T_Prestamos[],$M$5,FALSE)=0,"",VLOOKUP(C18,T_Prestamos[],$M$5,FALSE))</f>
-        <v>Al día</v>
+        <v/>
       </c>
       <c r="O18" s="50">
         <f>VLOOKUP(C18,T_Prestamos[],$N$5,FALSE)</f>
-        <v>38508.32</v>
+        <v>0</v>
       </c>
       <c r="P18" s="50">
         <f>VLOOKUP(C18,T_Prestamos[],$P$5,FALSE)</f>
-        <v>3963.8757846049866</v>
-      </c>
-      <c r="Q18" s="89">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="88">
         <f>VLOOKUP(C18,T_Prestamos[],$J$5,FALSE)</f>
-        <v>200000</v>
-      </c>
-      <c r="R18" s="90">
+        <v>300000</v>
+      </c>
+      <c r="R18" s="89">
         <f>VLOOKUP(C18,T_Prestamos[],$Q$5,FALSE)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="59" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="D19" s="46">
-        <v>0.25</v>
-      </c>
-      <c r="E19" s="48">
-        <f>L19*D19</f>
-        <v>20000</v>
-      </c>
-      <c r="F19" s="46">
-        <v>0.02</v>
-      </c>
-      <c r="G19" s="48">
-        <f>T_CCP[[#This Row],[Ingr. Anuales prest.]]*T_CCP[[#This Row],[% participación]]</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A19" s="23"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20" s="80" t="s">
+        <v>245</v>
+      </c>
+      <c r="B20" s="80"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="80"/>
+      <c r="R20" s="80"/>
+      <c r="S20" s="80"/>
+    </row>
+    <row r="21" spans="1:19" s="22" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A21" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="H21" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="I21" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="J21" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="K21" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="L21" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="M21" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="N21" s="36" t="s">
+        <v>262</v>
+      </c>
+      <c r="O21" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="P21" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q21" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="R21" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="S21" s="36" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="B22" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="C22" s="82">
+        <f>IF(A22=A21,C21+1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D22" s="47">
+        <v>1</v>
+      </c>
+      <c r="E22" s="47">
+        <v>3</v>
+      </c>
+      <c r="F22" s="51">
+        <f t="shared" ref="F22:F26" si="0">EDATE(S22,D22)</f>
+        <v>45488</v>
+      </c>
+      <c r="G22" s="51">
+        <f>EDATE(S22,E22)</f>
+        <v>45550</v>
+      </c>
+      <c r="H22" s="53" t="s">
+        <v>218</v>
+      </c>
+      <c r="I22" s="54">
+        <f>ROUND(IF(Q22="Americano",P22*O22/12*(T_Acciones_Prestamos[[#This Row],[Cuota_fin]]-T_Acciones_Prestamos[[#This Row],[Cuota_ini]]+1),-CUMIPMT(O22/12,R22,P22,D22,E22,0)),2)</f>
+        <v>1500</v>
+      </c>
+      <c r="J22" s="55">
+        <f t="shared" ref="J22:J26" si="1">ROUND(IF(Q22="Americano",0,-CUMPRINC(O22/12,R22,P22,D22,E22,0)),2)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="48">
-        <f>IF(T_CCP[[#This Row],[Estado final]]="Activo",E19*F19,0)</f>
+      <c r="K22" s="60">
+        <f>IF(T_Acciones_Prestamos[[#This Row],[Descripción]]="Cancelación del préstamo",P22,0)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="48">
-        <f>T_CCP[[#This Row],[Garantías prestamo]]*T_CCP[[#This Row],[% participación]]</f>
-        <v>75000</v>
-      </c>
-      <c r="J19" s="48">
-        <f>T_CCP[[#This Row],[Principal final]]*T_CCP[[#This Row],[% participación]]</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="49">
-        <f>VLOOKUP(C19,$A$8:$L$12,$F$5,FALSE)</f>
-        <v>0.09</v>
-      </c>
-      <c r="L19" s="50">
-        <f>VLOOKUP(C19,$A$8:$L$12,$C$5,FALSE)</f>
-        <v>80000</v>
-      </c>
-      <c r="M19" s="50" t="str">
-        <f>IF(VLOOKUP(C19,T_Prestamos[],$L$5,FALSE)=0,"",VLOOKUP(C19,T_Prestamos[],$L$5,FALSE))</f>
-        <v>Cancelado</v>
-      </c>
-      <c r="N19" s="50" t="str">
-        <f>IF(VLOOKUP(C19,T_Prestamos[],$M$5,FALSE)=0,"",VLOOKUP(C19,T_Prestamos[],$M$5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O19" s="50">
-        <f>VLOOKUP(C19,T_Prestamos[],$N$5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="P19" s="50">
-        <f>VLOOKUP(C19,T_Prestamos[],$P$5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="89">
-        <f>VLOOKUP(C19,T_Prestamos[],$J$5,FALSE)</f>
-        <v>300000</v>
-      </c>
-      <c r="R19" s="90">
-        <f>VLOOKUP(C19,T_Prestamos[],$Q$5,FALSE)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A21" s="81" t="s">
-        <v>252</v>
-      </c>
-      <c r="B21" s="81"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="81"/>
-      <c r="N21" s="81"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="81"/>
-      <c r="R21" s="81"/>
-      <c r="S21" s="81"/>
-    </row>
-    <row r="22" spans="1:19" s="22" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A22" s="36" t="s">
-        <v>213</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>255</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>240</v>
-      </c>
-      <c r="G22" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="H22" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="I22" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="J22" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="K22" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="L22" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="M22" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="N22" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="O22" s="36" t="s">
-        <v>228</v>
-      </c>
-      <c r="P22" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q22" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="R22" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="S22" s="36" t="s">
-        <v>241</v>
+      <c r="L22" s="60"/>
+      <c r="M22" s="56">
+        <f>P22-J22</f>
+        <v>100000</v>
+      </c>
+      <c r="N22" s="56"/>
+      <c r="O22" s="49">
+        <f t="shared" ref="O22:O27" si="2">VLOOKUP(A22,$A$8:$Q$11,$F$5,FALSE)</f>
+        <v>0.06</v>
+      </c>
+      <c r="P22" s="50">
+        <f>VLOOKUP(A22,$A$8:$Q$11,$C$5,FALSE)</f>
+        <v>100000</v>
+      </c>
+      <c r="Q22" s="50" t="str">
+        <f t="shared" ref="Q22:Q27" si="3">VLOOKUP(A22,$A$8:$Q$11,$E$5,FALSE)</f>
+        <v>Americano</v>
+      </c>
+      <c r="R22" s="57">
+        <f t="shared" ref="R22:R27" si="4">VLOOKUP(A22,$A$8:$Q$11,$G$5,FALSE)</f>
+        <v>36</v>
+      </c>
+      <c r="S22" s="59">
+        <f t="shared" ref="S22:S27" si="5">VLOOKUP(A22,$A$8:$Q$11,$D$5,FALSE)</f>
+        <v>45458</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="B23" s="59" t="s">
-        <v>221</v>
-      </c>
-      <c r="C23" s="83">
-        <f>IF(A23=A22,C22+1,1)</f>
-        <v>1</v>
+        <v>206</v>
+      </c>
+      <c r="B23" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" s="82">
+        <f t="shared" ref="C23:C26" si="6">IF(A23=A22,C22+1,1)</f>
+        <v>2</v>
       </c>
       <c r="D23" s="47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="51">
-        <f t="shared" ref="F23:F29" si="0">EDATE(S23,D23)</f>
-        <v>45488</v>
-      </c>
-      <c r="G23" s="51">
-        <f>EDATE(S23,E23)</f>
-        <v>45550</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>45580</v>
+      </c>
+      <c r="G23" s="52"/>
       <c r="H23" s="53" t="s">
-        <v>222</v>
-      </c>
-      <c r="I23" s="54">
+        <v>229</v>
+      </c>
+      <c r="I23" s="55">
         <f>ROUND(IF(Q23="Americano",P23*O23/12*(T_Acciones_Prestamos[[#This Row],[Cuota_fin]]-T_Acciones_Prestamos[[#This Row],[Cuota_ini]]+1),-CUMIPMT(O23/12,R23,P23,D23,E23,0)),2)</f>
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="J23" s="55">
-        <f t="shared" ref="J23:J29" si="1">ROUND(IF(Q23="Americano",0,-CUMPRINC(O23/12,R23,P23,D23,E23,0)),2)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K23" s="61">
         <f>IF(T_Acciones_Prestamos[[#This Row],[Descripción]]="Cancelación del préstamo",P23,0)</f>
+        <v>100000</v>
+      </c>
+      <c r="L23" s="60"/>
+      <c r="M23" s="56">
+        <f>P23-J23-K23</f>
         <v>0</v>
-      </c>
-      <c r="L23" s="61"/>
-      <c r="M23" s="56">
-        <f>P23-J23</f>
-        <v>100000</v>
       </c>
       <c r="N23" s="56"/>
       <c r="O23" s="49">
-        <f t="shared" ref="O23:O29" si="2">VLOOKUP(A23,$A$8:$Q$12,$F$5,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="P23" s="50">
-        <f>VLOOKUP(A23,$A$8:$Q$12,$C$5,FALSE)</f>
+        <f>VLOOKUP(A23,$A$8:$L$11,3,FALSE)</f>
         <v>100000</v>
       </c>
       <c r="Q23" s="50" t="str">
-        <f t="shared" ref="Q23:Q29" si="3">VLOOKUP(A23,$A$8:$Q$12,$E$5,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>Americano</v>
       </c>
       <c r="R23" s="57">
-        <f t="shared" ref="R23:R29" si="4">VLOOKUP(A23,$A$8:$Q$12,$G$5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="S23" s="60">
-        <f t="shared" ref="S23:S29" si="5">VLOOKUP(A23,$A$8:$Q$12,$D$5,FALSE)</f>
+      <c r="S23" s="59">
+        <f t="shared" si="5"/>
         <v>45458</v>
       </c>
     </row>
@@ -5595,74 +6207,77 @@
       <c r="A24" s="47" t="s">
         <v>210</v>
       </c>
-      <c r="B24" s="59" t="s">
-        <v>232</v>
-      </c>
-      <c r="C24" s="83">
-        <f t="shared" ref="C24:C29" si="6">IF(A24=A23,C23+1,1)</f>
-        <v>2</v>
+      <c r="B24" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="C24" s="82">
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="D24" s="47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E24" s="47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" s="51">
         <f t="shared" si="0"/>
-        <v>45580</v>
-      </c>
-      <c r="G24" s="52"/>
+        <v>45920</v>
+      </c>
+      <c r="G24" s="51">
+        <f t="shared" ref="G24:G26" si="7">EDATE(S24,E24)</f>
+        <v>45981</v>
+      </c>
       <c r="H24" s="53" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="I24" s="55">
         <f>ROUND(IF(Q24="Americano",P24*O24/12*(T_Acciones_Prestamos[[#This Row],[Cuota_fin]]-T_Acciones_Prestamos[[#This Row],[Cuota_ini]]+1),-CUMIPMT(O24/12,R24,P24,D24,E24,0)),2)</f>
-        <v>500</v>
+        <v>1178.6600000000001</v>
       </c>
       <c r="J24" s="55">
         <f t="shared" si="1"/>
+        <v>3215.67</v>
+      </c>
+      <c r="K24" s="60">
+        <f>IF(T_Acciones_Prestamos[[#This Row],[Descripción]]="Cancelación del préstamo",P24,0)</f>
         <v>0</v>
       </c>
-      <c r="K24" s="62">
-        <f>IF(T_Acciones_Prestamos[[#This Row],[Descripción]]="Cancelación del préstamo",P24,0)</f>
-        <v>100000</v>
-      </c>
-      <c r="L24" s="61"/>
+      <c r="L24" s="60"/>
       <c r="M24" s="56">
-        <f>P24-J24-K24</f>
-        <v>0</v>
+        <f>P24-J24</f>
+        <v>56784.33</v>
       </c>
       <c r="N24" s="56"/>
       <c r="O24" s="49">
         <f t="shared" si="2"/>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="P24" s="50">
-        <f t="shared" ref="P24:P29" si="7">VLOOKUP(A24,$A$8:$L$12,3,FALSE)</f>
-        <v>100000</v>
+        <f>VLOOKUP(A24,$A$8:$L$11,3,FALSE)</f>
+        <v>60000</v>
       </c>
       <c r="Q24" s="50" t="str">
         <f t="shared" si="3"/>
-        <v>Americano</v>
+        <v>Francés</v>
       </c>
       <c r="R24" s="57">
         <f t="shared" si="4"/>
-        <v>36</v>
-      </c>
-      <c r="S24" s="60">
+        <v>48</v>
+      </c>
+      <c r="S24" s="59">
         <f t="shared" si="5"/>
-        <v>45458</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="47" t="s">
-        <v>214</v>
-      </c>
-      <c r="B25" s="59" t="s">
-        <v>221</v>
-      </c>
-      <c r="C25" s="83">
+        <v>140</v>
+      </c>
+      <c r="B25" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="C25" s="82">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -5670,66 +6285,66 @@
         <v>1</v>
       </c>
       <c r="E25" s="47">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F25" s="51">
         <f t="shared" si="0"/>
-        <v>45920</v>
+        <v>45570</v>
       </c>
       <c r="G25" s="51">
-        <f t="shared" ref="G25:G29" si="8">EDATE(S25,E25)</f>
-        <v>46466</v>
+        <f t="shared" si="7"/>
+        <v>45631</v>
       </c>
       <c r="H25" s="53" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I25" s="55">
         <f>ROUND(IF(Q25="Americano",P25*O25/12*(T_Acciones_Prestamos[[#This Row],[Cuota_fin]]-T_Acciones_Prestamos[[#This Row],[Cuota_ini]]+1),-CUMIPMT(O25/12,R25,P25,D25,E25,0)),2)</f>
-        <v>6339.05</v>
+        <v>1800</v>
       </c>
       <c r="J25" s="55">
         <f t="shared" si="1"/>
-        <v>21491.68</v>
-      </c>
-      <c r="K25" s="61">
+        <v>0</v>
+      </c>
+      <c r="K25" s="60">
         <f>IF(T_Acciones_Prestamos[[#This Row],[Descripción]]="Cancelación del préstamo",P25,0)</f>
         <v>0</v>
       </c>
-      <c r="L25" s="61"/>
+      <c r="L25" s="60"/>
       <c r="M25" s="56">
         <f>P25-J25</f>
-        <v>38508.32</v>
+        <v>80000</v>
       </c>
       <c r="N25" s="56"/>
       <c r="O25" s="49">
         <f t="shared" si="2"/>
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="P25" s="50">
-        <f t="shared" si="7"/>
-        <v>60000</v>
+        <f>VLOOKUP(A25,$A$8:$L$11,3,FALSE)</f>
+        <v>80000</v>
       </c>
       <c r="Q25" s="50" t="str">
         <f t="shared" si="3"/>
-        <v>Francés</v>
+        <v>Americano</v>
       </c>
       <c r="R25" s="57">
         <f t="shared" si="4"/>
-        <v>48</v>
-      </c>
-      <c r="S25" s="60">
+        <v>60</v>
+      </c>
+      <c r="S25" s="59">
         <f t="shared" si="5"/>
-        <v>45889</v>
+        <v>45540</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="B26" s="59" t="s">
         <v>221</v>
       </c>
-      <c r="C26" s="83">
+      <c r="B26" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="C26" s="82">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -5741,466 +6356,379 @@
       </c>
       <c r="F26" s="51">
         <f t="shared" si="0"/>
-        <v>45570</v>
+        <v>45606</v>
       </c>
       <c r="G26" s="51">
-        <f t="shared" si="8"/>
-        <v>45631</v>
+        <f t="shared" si="7"/>
+        <v>45667</v>
       </c>
       <c r="H26" s="53" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I26" s="55">
         <f>ROUND(IF(Q26="Americano",P26*O26/12*(T_Acciones_Prestamos[[#This Row],[Cuota_fin]]-T_Acciones_Prestamos[[#This Row],[Cuota_ini]]+1),-CUMIPMT(O26/12,R26,P26,D26,E26,0)),2)</f>
-        <v>1800</v>
+        <v>1560.44</v>
       </c>
       <c r="J26" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="61">
+        <v>5960.29</v>
+      </c>
+      <c r="K26" s="60">
         <f>IF(T_Acciones_Prestamos[[#This Row],[Descripción]]="Cancelación del préstamo",P26,0)</f>
         <v>0</v>
       </c>
-      <c r="L26" s="61"/>
+      <c r="L26" s="60"/>
       <c r="M26" s="56">
         <f>P26-J26</f>
-        <v>80000</v>
+        <v>74039.710000000006</v>
       </c>
       <c r="N26" s="56"/>
       <c r="O26" s="49">
         <f t="shared" si="2"/>
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="P26" s="50">
-        <f t="shared" si="7"/>
+        <f>VLOOKUP(A26,$A$8:$L$11,3,FALSE)</f>
         <v>80000</v>
       </c>
       <c r="Q26" s="50" t="str">
         <f t="shared" si="3"/>
-        <v>Americano</v>
+        <v>Francés</v>
       </c>
       <c r="R26" s="57">
         <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="S26" s="60">
+        <v>36</v>
+      </c>
+      <c r="S26" s="59">
         <f t="shared" si="5"/>
-        <v>45540</v>
+        <v>45575</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="B27" s="59" t="s">
-        <v>239</v>
-      </c>
-      <c r="C27" s="83">
-        <f t="shared" si="6"/>
+        <v>221</v>
+      </c>
+      <c r="B27" s="58" t="s">
+        <v>290</v>
+      </c>
+      <c r="C27" s="82">
+        <f>IF(A27=A26,C26+1,1)</f>
         <v>2</v>
       </c>
       <c r="D27" s="47">
         <v>4</v>
       </c>
       <c r="E27" s="47">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F27" s="51">
-        <f t="shared" si="0"/>
-        <v>45662</v>
+        <f>EDATE(S27,D27)</f>
+        <v>45698</v>
       </c>
       <c r="G27" s="51">
-        <f t="shared" si="8"/>
-        <v>45782</v>
+        <f>EDATE(S27,E27)</f>
+        <v>45757</v>
       </c>
       <c r="H27" s="53" t="s">
-        <v>242</v>
-      </c>
-      <c r="I27" s="55">
+        <v>289</v>
+      </c>
+      <c r="I27" s="126">
         <f>ROUND(IF(Q27="Americano",P27*O27/12*(T_Acciones_Prestamos[[#This Row],[Cuota_fin]]-T_Acciones_Prestamos[[#This Row],[Cuota_ini]]+1),-CUMIPMT(O27/12,R27,P27,D27,E27,0)),2)</f>
-        <v>3000</v>
-      </c>
-      <c r="J27" s="55">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="58">
-        <v>50000</v>
-      </c>
-      <c r="L27" s="61"/>
+        <v>1440.44</v>
+      </c>
+      <c r="J27" s="126">
+        <f>ROUND(IF(Q27="Americano",0,-CUMPRINC(O27/12,R27,P27,D27,E27,0)),2)</f>
+        <v>6080.29</v>
+      </c>
+      <c r="K27" s="61">
+        <f>M26</f>
+        <v>74039.710000000006</v>
+      </c>
+      <c r="L27" s="127"/>
       <c r="M27" s="56">
-        <f>P27-J27-K27</f>
-        <v>30000</v>
+        <f>IF(T_Acciones_Prestamos[[#This Row],[Acción]]="Judicializar",T_Acciones_Prestamos[[#This Row],[Cancelación
+Judicialización
+Amortización parcial]],T_Acciones_Prestamos[[#This Row],[Aux Principal]]-T_Acciones_Prestamos[[#This Row],[Principal]]-T_Acciones_Prestamos[[#This Row],[Cancelación
+Judicialización
+Amortización parcial]])</f>
+        <v>74039.710000000006</v>
       </c>
       <c r="N27" s="56"/>
       <c r="O27" s="49">
         <f t="shared" si="2"/>
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="P27" s="50">
-        <f t="shared" si="7"/>
+        <f>VLOOKUP(A27,$A$8:$L$11,3,FALSE)</f>
         <v>80000</v>
       </c>
       <c r="Q27" s="50" t="str">
         <f t="shared" si="3"/>
-        <v>Americano</v>
+        <v>Francés</v>
       </c>
       <c r="R27" s="57">
         <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="S27" s="60">
-        <f t="shared" si="5"/>
-        <v>45540</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="B28" s="59" t="s">
-        <v>243</v>
-      </c>
-      <c r="C28" s="83">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="D28" s="47">
-        <v>1</v>
-      </c>
-      <c r="E28" s="47">
-        <v>5</v>
-      </c>
-      <c r="F28" s="51">
-        <f t="shared" si="0"/>
-        <v>45813</v>
-      </c>
-      <c r="G28" s="51">
-        <f t="shared" si="8"/>
-        <v>45935</v>
-      </c>
-      <c r="H28" s="53" t="s">
-        <v>243</v>
-      </c>
-      <c r="I28" s="55">
-        <f>ROUND(IF(Q28="Americano",P28*O28/12*(T_Acciones_Prestamos[[#This Row],[Cuota_fin]]-T_Acciones_Prestamos[[#This Row],[Cuota_ini]]+1),-CUMIPMT(O28/12,R28,P28,D28,E28,0)),2)</f>
-        <v>1125</v>
-      </c>
-      <c r="J28" s="55">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="61">
-        <f>IF(T_Acciones_Prestamos[[#This Row],[Descripción]]="Cancelación del préstamo",P28,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L28" s="82">
-        <f>T_Acciones_Prestamos[[#This Row],[Aux Principal]]+T_Acciones_Prestamos[[#This Row],[Intereses]]</f>
-        <v>31125</v>
-      </c>
-      <c r="M28" s="56">
-        <f>P28-J28-K28</f>
-        <v>30000</v>
-      </c>
-      <c r="N28" s="56"/>
-      <c r="O28" s="49">
-        <f t="shared" si="2"/>
-        <v>0.09</v>
-      </c>
-      <c r="P28" s="50">
-        <f t="shared" si="7"/>
-        <v>30000</v>
-      </c>
-      <c r="Q28" s="50" t="str">
-        <f t="shared" si="3"/>
-        <v>Americano</v>
-      </c>
-      <c r="R28" s="57">
-        <f t="shared" si="4"/>
-        <v>52</v>
-      </c>
-      <c r="S28" s="60">
-        <f t="shared" si="5"/>
-        <v>45782</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="B29" s="59" t="s">
-        <v>221</v>
-      </c>
-      <c r="C29" s="83">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="D29" s="47">
-        <v>1</v>
-      </c>
-      <c r="E29" s="47">
-        <v>3</v>
-      </c>
-      <c r="F29" s="51">
-        <f t="shared" si="0"/>
-        <v>45606</v>
-      </c>
-      <c r="G29" s="51">
-        <f t="shared" si="8"/>
-        <v>45667</v>
-      </c>
-      <c r="H29" s="53" t="s">
-        <v>222</v>
-      </c>
-      <c r="I29" s="55">
-        <f>ROUND(IF(Q29="Americano",P29*O29/12*(T_Acciones_Prestamos[[#This Row],[Cuota_fin]]-T_Acciones_Prestamos[[#This Row],[Cuota_ini]]+1),-CUMIPMT(O29/12,R29,P29,D29,E29,0)),2)</f>
-        <v>1560.44</v>
-      </c>
-      <c r="J29" s="55">
-        <f t="shared" si="1"/>
-        <v>5960.29</v>
-      </c>
-      <c r="K29" s="61">
-        <f>IF(T_Acciones_Prestamos[[#This Row],[Descripción]]="Cancelación del préstamo",P29,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="61"/>
-      <c r="M29" s="56">
-        <f>P29-J29</f>
-        <v>74039.710000000006</v>
-      </c>
-      <c r="N29" s="56"/>
-      <c r="O29" s="49">
-        <f t="shared" si="2"/>
-        <v>0.08</v>
-      </c>
-      <c r="P29" s="50">
-        <f t="shared" si="7"/>
-        <v>80000</v>
-      </c>
-      <c r="Q29" s="50" t="str">
-        <f t="shared" si="3"/>
-        <v>Francés</v>
-      </c>
-      <c r="R29" s="57">
-        <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="S29" s="60">
+      <c r="S27" s="59">
         <f t="shared" si="5"/>
         <v>45575</v>
       </c>
     </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A28" s="69"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="50"/>
+      <c r="P28" s="57"/>
+      <c r="Q28" s="59"/>
+    </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A30" s="70"/>
-      <c r="B30" s="64"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="69"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="57"/>
-      <c r="Q30" s="60"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A32" s="81" t="s">
-        <v>248</v>
-      </c>
-      <c r="B32" s="81"/>
-      <c r="C32" s="106"/>
-      <c r="D32" s="81"/>
-    </row>
-    <row r="33" spans="1:17" s="22" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="36" t="s">
+      <c r="A30" s="80" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="80"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="80"/>
+    </row>
+    <row r="31" spans="1:19" s="22" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A31" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="B31" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="A32" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="B32" s="85" t="s">
+        <v>244</v>
+      </c>
+      <c r="C32" s="97">
+        <f>SUMIFS(C8:C11,L8:L11,"Cancelado")</f>
+        <v>180000</v>
+      </c>
+      <c r="D32" s="26"/>
+    </row>
+    <row r="33" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+      <c r="A33" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="B33" s="85" t="s">
+        <v>246</v>
+      </c>
+      <c r="C33" s="97">
+        <f>SUM(T_Prestamos[Principal])-SUMIFS(C8:C11,L8:L11,"Cancelado")</f>
+        <v>140000</v>
+      </c>
+      <c r="D33" s="26"/>
+    </row>
+    <row r="34" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+      <c r="A34" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B34" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="C34" s="97">
+        <f>SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Activo")+SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Judicializado")</f>
+        <v>130824.04000000001</v>
+      </c>
+      <c r="D34" s="26"/>
+    </row>
+    <row r="35" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+      <c r="A35" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="B35" s="85" t="s">
         <v>250</v>
       </c>
-      <c r="B33" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="D33" s="36" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A34" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="B34" s="86" t="s">
+      <c r="C35" s="97">
+        <f>SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Activo")</f>
+        <v>56784.33</v>
+      </c>
+      <c r="D35" s="26"/>
+    </row>
+    <row r="36" spans="1:17" ht="85" x14ac:dyDescent="0.2">
+      <c r="A36" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="B36" s="85" t="s">
         <v>251</v>
       </c>
-      <c r="C34" s="107">
-        <f>SUMIFS(C8:C12,L8:L12,"Cancelado")</f>
-        <v>180000</v>
-      </c>
-      <c r="D34" s="26"/>
-    </row>
-    <row r="35" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A35" s="41" t="s">
-        <v>247</v>
-      </c>
-      <c r="B35" s="86" t="s">
+      <c r="C36" s="97">
+        <f>SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Activo",T_Prestamos[Situación final],"Al día")</f>
+        <v>56784.33</v>
+      </c>
+      <c r="D36" s="26"/>
+    </row>
+    <row r="37" spans="1:17" ht="85" x14ac:dyDescent="0.2">
+      <c r="A37" s="41" t="s">
+        <v>239</v>
+      </c>
+      <c r="B37" s="85" t="s">
+        <v>251</v>
+      </c>
+      <c r="C37" s="97">
+        <f>SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Activo",T_Prestamos[Situación final],"Con retraso")</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="26"/>
+    </row>
+    <row r="38" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+      <c r="A38" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" s="85" t="s">
+        <v>252</v>
+      </c>
+      <c r="C38" s="97">
+        <f>SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Judicializado")</f>
+        <v>74039.710000000006</v>
+      </c>
+      <c r="D38" s="26"/>
+    </row>
+    <row r="39" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+      <c r="A39" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="C35" s="107">
-        <f>SUM(T_Prestamos[Principal])-SUMIFS(C8:C12,L8:L12,"Cancelado")</f>
-        <v>170000</v>
-      </c>
-      <c r="D35" s="26"/>
-    </row>
-    <row r="36" spans="1:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="A36" s="41" t="s">
-        <v>141</v>
-      </c>
-      <c r="B36" s="86" t="s">
+      <c r="B39" s="85" t="s">
         <v>256</v>
       </c>
-      <c r="C36" s="107">
-        <f>SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Activo")+SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Judicializado")</f>
-        <v>142548.03</v>
-      </c>
-      <c r="D36" s="26"/>
-    </row>
-    <row r="37" spans="1:17" ht="68" x14ac:dyDescent="0.2">
-      <c r="A37" s="41" t="s">
-        <v>237</v>
-      </c>
-      <c r="B37" s="86" t="s">
-        <v>257</v>
-      </c>
-      <c r="C37" s="107">
-        <f>SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Activo")</f>
-        <v>112548.03</v>
-      </c>
-      <c r="D37" s="26"/>
-    </row>
-    <row r="38" spans="1:17" ht="85" x14ac:dyDescent="0.2">
-      <c r="A38" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="B38" s="86" t="s">
-        <v>258</v>
-      </c>
-      <c r="C38" s="107">
-        <f>SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Activo",T_Prestamos[Situación final],"Al día")</f>
-        <v>38508.32</v>
-      </c>
-      <c r="D38" s="26"/>
-    </row>
-    <row r="39" spans="1:17" ht="85" x14ac:dyDescent="0.2">
-      <c r="A39" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="B39" s="86" t="s">
-        <v>258</v>
-      </c>
-      <c r="C39" s="107">
-        <f>SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Activo",T_Prestamos[Situación final],"Con retraso")</f>
-        <v>74039.710000000006</v>
+      <c r="C39" s="97">
+        <f>SUMIFS(T_CCP[Participado final],T_CCP[Estado final],"Activo")</f>
+        <v>28392.165000000001</v>
       </c>
       <c r="D39" s="26"/>
     </row>
     <row r="40" spans="1:17" ht="68" x14ac:dyDescent="0.2">
       <c r="A40" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="B40" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="C40" s="107">
-        <f>SUMIFS(T_Prestamos[Principal final],T_Prestamos[Estado final],"Judicializado")</f>
-        <v>30000</v>
+        <v>254</v>
+      </c>
+      <c r="B40" s="85" t="s">
+        <v>255</v>
+      </c>
+      <c r="C40" s="97">
+        <f>SUMIFS(T_CCP[Participado final],T_CCP[Estado final],"Judicializado")</f>
+        <v>0</v>
       </c>
       <c r="D40" s="26"/>
     </row>
-    <row r="41" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" ht="51" x14ac:dyDescent="0.2">
       <c r="A41" s="41" t="s">
         <v>260</v>
       </c>
-      <c r="B41" s="86" t="s">
-        <v>263</v>
-      </c>
-      <c r="C41" s="107">
-        <f>SUMIFS(T_CCP[Participado final],T_CCP[Estado final],"Activo")</f>
-        <v>19254.16</v>
+      <c r="B41" s="85" t="s">
+        <v>259</v>
+      </c>
+      <c r="C41" s="97">
+        <f>SUMIFS(T_Prestamos[Ingr. Anuales],T_Prestamos[Estado final],"Activo")</f>
+        <v>3963.8757846049866</v>
       </c>
       <c r="D41" s="26"/>
     </row>
-    <row r="42" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" ht="51" x14ac:dyDescent="0.2">
       <c r="A42" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="B42" s="86" t="s">
-        <v>262</v>
-      </c>
-      <c r="C42" s="107">
-        <f>SUMIFS(T_CCP[Participado final],T_CCP[Estado final],"Judicializado")</f>
-        <v>0</v>
+      <c r="B42" s="85" t="s">
+        <v>259</v>
+      </c>
+      <c r="C42" s="97">
+        <f>SUMIFS(T_CCP[Ingresos anuales],T_CCP[Estado final],"Activo")</f>
+        <v>1981.9378923024933</v>
       </c>
       <c r="D42" s="26"/>
     </row>
-    <row r="43" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A43" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="B43" s="86" t="s">
-        <v>266</v>
-      </c>
-      <c r="C43" s="107">
-        <f>SUMIFS(T_Prestamos[Ingr. Anuales],T_Prestamos[Estado final],"Activo")</f>
-        <v>7080.5562708968337</v>
+      <c r="B43" s="85" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" s="97">
+        <f>SUM(T_CCP[Gestión])</f>
+        <v>567.8433</v>
       </c>
       <c r="D43" s="26"/>
     </row>
-    <row r="44" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A44" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="B44" s="86" t="s">
-        <v>266</v>
-      </c>
-      <c r="C44" s="107">
-        <f>SUMIFS(T_CCP[Ingresos anuales],T_CCP[Estado final],"Activo")</f>
-        <v>1981.9378923024933</v>
+        <v>145</v>
+      </c>
+      <c r="B44" s="85" t="s">
+        <v>272</v>
+      </c>
+      <c r="C44" s="97">
+        <f>SUMIFS(T_Prestamos[Garantía],T_Prestamos[Estado final],"Activo")+SUMIFS(T_Prestamos[Garantía],T_Prestamos[Estado final],"Judicializado")</f>
+        <v>450000</v>
       </c>
       <c r="D44" s="26"/>
-    </row>
-    <row r="45" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="49"/>
+      <c r="L44" s="49"/>
+      <c r="M44" s="49"/>
+      <c r="N44" s="50"/>
+      <c r="O44" s="50"/>
+      <c r="P44" s="57"/>
+      <c r="Q44" s="59"/>
+    </row>
+    <row r="45" spans="1:17" ht="51" x14ac:dyDescent="0.2">
       <c r="A45" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="B45" s="85" t="s">
         <v>274</v>
       </c>
-      <c r="B45" s="86" t="s">
-        <v>275</v>
-      </c>
-      <c r="C45" s="107">
-        <f>SUM(T_CCP[Gestión])</f>
-        <v>600</v>
+      <c r="C45" s="97">
+        <f>SUMIFS(T_CCP[Garantías part.],T_CCP[Estado final],"Activo")+SUMIFS(T_CCP[Garantías part.],T_CCP[Estado final],"Judicializado")</f>
+        <v>100000</v>
       </c>
       <c r="D45" s="26"/>
-    </row>
-    <row r="46" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A46" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="B46" s="86" t="s">
-        <v>279</v>
-      </c>
-      <c r="C46" s="107">
-        <f>SUMIFS(T_Prestamos[Garantía],T_Prestamos[Estado final],"Activo")+SUMIFS(T_Prestamos[Garantía],T_Prestamos[Estado final],"Judicializado")</f>
-        <v>750000</v>
-      </c>
-      <c r="D46" s="26"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="49"/>
+      <c r="I45" s="49"/>
+      <c r="J45" s="49"/>
+      <c r="K45" s="49"/>
+      <c r="L45" s="49"/>
+      <c r="M45" s="49"/>
+      <c r="N45" s="50"/>
+      <c r="O45" s="50"/>
+      <c r="P45" s="57"/>
+      <c r="Q45" s="59"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A46" s="49"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="98"/>
+      <c r="D46" s="49"/>
       <c r="E46" s="49"/>
       <c r="F46" s="49"/>
       <c r="G46" s="49"/>
@@ -6213,601 +6741,556 @@
       <c r="N46" s="50"/>
       <c r="O46" s="50"/>
       <c r="P46" s="57"/>
-      <c r="Q46" s="60"/>
-    </row>
-    <row r="47" spans="1:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="A47" s="41" t="s">
-        <v>280</v>
-      </c>
-      <c r="B47" s="86" t="s">
-        <v>281</v>
-      </c>
-      <c r="C47" s="107">
-        <f>SUMIFS(T_CCP[Garantías part.],T_CCP[Estado final],"Activo")+SUMIFS(T_CCP[Garantías part.],T_CCP[Estado final],"Judicializado")</f>
-        <v>100000</v>
-      </c>
-      <c r="D47" s="26"/>
-      <c r="E47" s="49"/>
+      <c r="Q46" s="59"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="F47" s="49"/>
       <c r="G47" s="49"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="49"/>
-      <c r="K47" s="49"/>
-      <c r="L47" s="49"/>
-      <c r="M47" s="49"/>
-      <c r="N47" s="50"/>
-      <c r="O47" s="50"/>
-      <c r="P47" s="57"/>
-      <c r="Q47" s="60"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A48" s="49"/>
-      <c r="B48" s="49"/>
-      <c r="C48" s="108"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
+      <c r="A48" s="80" t="s">
+        <v>278</v>
+      </c>
+      <c r="B48" s="80"/>
+      <c r="C48" s="96"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="80"/>
       <c r="F48" s="49"/>
       <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
-      <c r="K48" s="49"/>
-      <c r="L48" s="49"/>
-      <c r="M48" s="49"/>
-      <c r="N48" s="50"/>
-      <c r="O48" s="50"/>
-      <c r="P48" s="57"/>
-      <c r="Q48" s="60"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A49" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="D49" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E49" s="36" t="s">
+        <v>16</v>
+      </c>
       <c r="F49" s="49"/>
       <c r="G49" s="49"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="81" t="s">
-        <v>285</v>
-      </c>
-      <c r="B50" s="81"/>
-      <c r="C50" s="106"/>
-      <c r="D50" s="81"/>
-      <c r="E50" s="81"/>
+    <row r="50" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A50" s="116" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" s="117" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="117" t="s">
+        <v>240</v>
+      </c>
+      <c r="D50" s="86">
+        <f>C33</f>
+        <v>140000</v>
+      </c>
+      <c r="E50" s="117"/>
       <c r="F50" s="49"/>
       <c r="G50" s="49"/>
     </row>
     <row r="51" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A51" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="B51" s="36" t="s">
+      <c r="A51" s="116" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" s="117" t="s">
         <v>124</v>
       </c>
-      <c r="C51" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E51" s="36" t="s">
-        <v>16</v>
-      </c>
+      <c r="C51" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" s="86">
+        <f>C34</f>
+        <v>130824.04000000001</v>
+      </c>
+      <c r="E51" s="117"/>
       <c r="F51" s="49"/>
       <c r="G51" s="49"/>
     </row>
     <row r="52" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A52" s="94" t="s">
-        <v>127</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C52" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="D52" s="87">
+      <c r="A52" s="116" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="117" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="117" t="s">
+        <v>233</v>
+      </c>
+      <c r="D52" s="86">
         <f>C35</f>
-        <v>170000</v>
-      </c>
-      <c r="E52" s="28"/>
+        <v>56784.33</v>
+      </c>
+      <c r="E52" s="117"/>
       <c r="F52" s="49"/>
       <c r="G52" s="49"/>
     </row>
     <row r="53" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A53" s="94" t="s">
-        <v>129</v>
-      </c>
-      <c r="B53" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C53" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="D53" s="87">
-        <f>C36</f>
-        <v>142548.03</v>
-      </c>
-      <c r="E53" s="28"/>
+      <c r="A53" s="116" t="s">
+        <v>127</v>
+      </c>
+      <c r="B53" s="117" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" s="117" t="s">
+        <v>189</v>
+      </c>
+      <c r="D53" s="86">
+        <f>C38</f>
+        <v>74039.710000000006</v>
+      </c>
+      <c r="E53" s="117"/>
       <c r="F53" s="49"/>
       <c r="G53" s="49"/>
     </row>
     <row r="54" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A54" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="B54" s="28" t="s">
+      <c r="A54" s="116" t="s">
         <v>128</v>
       </c>
-      <c r="C54" s="28" t="s">
-        <v>237</v>
+      <c r="B54" s="117" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" s="117" t="s">
+        <v>129</v>
       </c>
       <c r="D54" s="87">
-        <f>C37</f>
-        <v>112548.03</v>
-      </c>
-      <c r="E54" s="28"/>
+        <f>D53/(D53+D52)</f>
+        <v>0.56594881185445733</v>
+      </c>
+      <c r="E54" s="117"/>
       <c r="F54" s="49"/>
       <c r="G54" s="49"/>
     </row>
     <row r="55" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A55" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="B55" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C55" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="D55" s="87">
-        <f>C40</f>
-        <v>30000</v>
-      </c>
-      <c r="E55" s="28"/>
+      <c r="A55" s="116" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="117" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="117" t="s">
+        <v>253</v>
+      </c>
+      <c r="D55" s="86">
+        <f>C39</f>
+        <v>28392.165000000001</v>
+      </c>
+      <c r="E55" s="117"/>
       <c r="F55" s="49"/>
       <c r="G55" s="49"/>
     </row>
     <row r="56" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A56" s="94" t="s">
-        <v>132</v>
-      </c>
-      <c r="B56" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C56" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D56" s="88">
-        <f>D55/(D55+D54)</f>
-        <v>0.21045538124939361</v>
-      </c>
-      <c r="E56" s="28"/>
+      <c r="A56" s="116" t="s">
+        <v>184</v>
+      </c>
+      <c r="B56" s="117" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56" s="117" t="s">
+        <v>254</v>
+      </c>
+      <c r="D56" s="86">
+        <f>C40</f>
+        <v>0</v>
+      </c>
+      <c r="E56" s="117"/>
       <c r="F56" s="49"/>
       <c r="G56" s="49"/>
     </row>
     <row r="57" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A57" s="94" t="s">
-        <v>134</v>
-      </c>
-      <c r="B57" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C57" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="D57" s="87">
-        <f>C41</f>
-        <v>19254.16</v>
-      </c>
-      <c r="E57" s="28"/>
+      <c r="A57" s="118" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" s="119" t="s">
+        <v>129</v>
+      </c>
+      <c r="D57" s="91">
+        <f>D56/(D55+D56)</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="119"/>
       <c r="F57" s="49"/>
       <c r="G57" s="49"/>
     </row>
     <row r="58" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A58" s="94" t="s">
+      <c r="A58" s="120" t="s">
+        <v>192</v>
+      </c>
+      <c r="B58" s="121" t="s">
+        <v>199</v>
+      </c>
+      <c r="C58" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="B58" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C58" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="D58" s="87">
-        <f>C42</f>
-        <v>0</v>
-      </c>
-      <c r="E58" s="28"/>
+      <c r="D58" s="92">
+        <f>C41</f>
+        <v>3963.8757846049866</v>
+      </c>
+      <c r="E58" s="121" t="s">
+        <v>265</v>
+      </c>
       <c r="F58" s="49"/>
       <c r="G58" s="49"/>
     </row>
-    <row r="59" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A59" s="95" t="s">
-        <v>189</v>
-      </c>
-      <c r="B59" s="96" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59" s="96" t="s">
-        <v>133</v>
-      </c>
-      <c r="D59" s="97">
-        <f>D58/(D57+D58)</f>
-        <v>0</v>
-      </c>
-      <c r="E59" s="96"/>
+    <row r="59" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A59" s="116" t="s">
+        <v>193</v>
+      </c>
+      <c r="B59" s="117" t="s">
+        <v>199</v>
+      </c>
+      <c r="C59" s="117" t="s">
+        <v>266</v>
+      </c>
+      <c r="D59" s="86">
+        <f>C42</f>
+        <v>1981.9378923024933</v>
+      </c>
+      <c r="E59" s="117" t="s">
+        <v>265</v>
+      </c>
       <c r="F59" s="49"/>
       <c r="G59" s="49"/>
     </row>
-    <row r="60" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A60" s="98" t="s">
-        <v>196</v>
-      </c>
-      <c r="B60" s="99" t="s">
-        <v>203</v>
-      </c>
-      <c r="C60" s="99" t="s">
-        <v>192</v>
-      </c>
-      <c r="D60" s="100">
+    <row r="60" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A60" s="116" t="s">
+        <v>194</v>
+      </c>
+      <c r="B60" s="117" t="s">
+        <v>199</v>
+      </c>
+      <c r="C60" s="117" t="s">
+        <v>269</v>
+      </c>
+      <c r="D60" s="86">
         <f>C43</f>
-        <v>7080.5562708968337</v>
-      </c>
-      <c r="E60" s="99" t="s">
-        <v>272</v>
-      </c>
+        <v>567.8433</v>
+      </c>
+      <c r="E60" s="117"/>
       <c r="F60" s="49"/>
       <c r="G60" s="49"/>
     </row>
     <row r="61" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A61" s="94" t="s">
-        <v>197</v>
-      </c>
-      <c r="B61" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="C61" s="28" t="s">
-        <v>273</v>
-      </c>
-      <c r="D61" s="87">
-        <f>C44</f>
-        <v>1981.9378923024933</v>
-      </c>
-      <c r="E61" s="28" t="s">
-        <v>272</v>
+      <c r="A61" s="116" t="s">
+        <v>195</v>
+      </c>
+      <c r="B61" s="117" t="s">
+        <v>199</v>
+      </c>
+      <c r="C61" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D61" s="86">
+        <f>SUM(T_Prestamos[Apertura])</f>
+        <v>1200</v>
+      </c>
+      <c r="E61" s="117" t="s">
+        <v>271</v>
       </c>
       <c r="F61" s="49"/>
       <c r="G61" s="49"/>
     </row>
-    <row r="62" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A62" s="94" t="s">
-        <v>198</v>
-      </c>
-      <c r="B62" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="C62" s="28" t="s">
-        <v>276</v>
+    <row r="62" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A62" s="116" t="s">
+        <v>196</v>
+      </c>
+      <c r="B62" s="117" t="s">
+        <v>199</v>
+      </c>
+      <c r="C62" s="117" t="s">
+        <v>277</v>
       </c>
       <c r="D62" s="87">
-        <f>C45</f>
-        <v>600</v>
-      </c>
-      <c r="E62" s="28"/>
+        <f>D58/D52</f>
+        <v>6.9805803548355444E-2</v>
+      </c>
+      <c r="E62" s="117"/>
       <c r="F62" s="49"/>
       <c r="G62" s="49"/>
     </row>
-    <row r="63" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A63" s="94" t="s">
+    <row r="63" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A63" s="116" t="s">
+        <v>197</v>
+      </c>
+      <c r="B63" s="117" t="s">
         <v>199</v>
       </c>
-      <c r="B63" s="28" t="s">
+      <c r="C63" s="117" t="s">
         <v>203</v>
       </c>
-      <c r="C63" s="28" t="s">
-        <v>277</v>
-      </c>
       <c r="D63" s="87">
-        <f>SUM(T_Prestamos[Apertura])</f>
-        <v>1200</v>
-      </c>
-      <c r="E63" s="28" t="s">
-        <v>278</v>
-      </c>
+        <f>D59/D55</f>
+        <v>6.9805803548355444E-2</v>
+      </c>
+      <c r="E63" s="117"/>
       <c r="F63" s="49"/>
       <c r="G63" s="49"/>
     </row>
-    <row r="64" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="94" t="s">
-        <v>200</v>
-      </c>
-      <c r="B64" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="C64" s="28" t="s">
-        <v>284</v>
-      </c>
-      <c r="D64" s="88">
-        <f>D60/D54</f>
-        <v>6.2911418981716816E-2</v>
-      </c>
-      <c r="E64" s="28"/>
+    <row r="64" spans="1:7" ht="102" x14ac:dyDescent="0.2">
+      <c r="A64" s="118" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" s="119" t="s">
+        <v>199</v>
+      </c>
+      <c r="C64" s="119" t="s">
+        <v>204</v>
+      </c>
+      <c r="D64" s="91">
+        <f>(D58-D59+D60+D61)/(D52-D55)</f>
+        <v>0.13207098480522683</v>
+      </c>
+      <c r="E64" s="119" t="s">
+        <v>280</v>
+      </c>
       <c r="F64" s="49"/>
       <c r="G64" s="49"/>
     </row>
     <row r="65" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A65" s="94" t="s">
-        <v>201</v>
-      </c>
-      <c r="B65" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="C65" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="D65" s="88">
-        <f>D61/D57</f>
-        <v>0.10293556780989113</v>
-      </c>
-      <c r="E65" s="28"/>
+      <c r="A65" s="122" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="123" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="123" t="s">
+        <v>133</v>
+      </c>
+      <c r="D65" s="90">
+        <f>COUNT(T_Prestamos[Principal])</f>
+        <v>4</v>
+      </c>
+      <c r="E65" s="123"/>
       <c r="F65" s="49"/>
       <c r="G65" s="49"/>
     </row>
-    <row r="66" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A66" s="95" t="s">
-        <v>202</v>
-      </c>
-      <c r="B66" s="96" t="s">
-        <v>203</v>
-      </c>
-      <c r="C66" s="96" t="s">
-        <v>208</v>
-      </c>
-      <c r="D66" s="97">
-        <f>(D60-D61+D62+D63)/(D54-D57)</f>
-        <v>7.3945033886946065E-2</v>
-      </c>
-      <c r="E66" s="96" t="s">
-        <v>287</v>
-      </c>
+    <row r="66" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A66" s="122" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="123" t="s">
+        <v>132</v>
+      </c>
+      <c r="C66" s="123" t="s">
+        <v>135</v>
+      </c>
+      <c r="D66" s="90">
+        <f>COUNTIFS(T_Prestamos[Estado final],"Cancelado")</f>
+        <v>2</v>
+      </c>
+      <c r="E66" s="123"/>
       <c r="F66" s="49"/>
       <c r="G66" s="49"/>
     </row>
     <row r="67" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" s="92" t="s">
-        <v>135</v>
-      </c>
-      <c r="B67" s="93" t="s">
+      <c r="A67" s="122" t="s">
         <v>136</v>
       </c>
-      <c r="C67" s="93" t="s">
+      <c r="B67" s="123" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" s="123" t="s">
         <v>137</v>
       </c>
-      <c r="D67" s="91">
-        <f>COUNT(T_Prestamos[Principal])</f>
-        <v>5</v>
-      </c>
-      <c r="E67" s="93"/>
+      <c r="D67" s="90">
+        <f>COUNTIFS(T_Prestamos[Estado final],"Activo")+COUNTIFS(T_Prestamos[Estado final],"Judicializado")</f>
+        <v>2</v>
+      </c>
+      <c r="E67" s="123"/>
       <c r="F67" s="49"/>
       <c r="G67" s="49"/>
     </row>
     <row r="68" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A68" s="92" t="s">
+      <c r="A68" s="122" t="s">
         <v>138</v>
       </c>
-      <c r="B68" s="93" t="s">
-        <v>136</v>
-      </c>
-      <c r="C68" s="93" t="s">
+      <c r="B68" s="123" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="123" t="s">
         <v>139</v>
       </c>
-      <c r="D68" s="91">
-        <f>COUNTIFS(T_Prestamos[Estado final],"Cancelado")</f>
-        <v>2</v>
-      </c>
-      <c r="E68" s="93"/>
+      <c r="D68" s="90">
+        <f>COUNTIFS(T_Prestamos[Estado final],"Judicializado")</f>
+        <v>1</v>
+      </c>
+      <c r="E68" s="123"/>
       <c r="F68" s="49"/>
       <c r="G68" s="49"/>
     </row>
     <row r="69" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A69" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="B69" s="93" t="s">
-        <v>136</v>
-      </c>
-      <c r="C69" s="93" t="s">
+      <c r="A69" s="124" t="s">
         <v>141</v>
       </c>
-      <c r="D69" s="91">
-        <f>COUNTIFS(T_Prestamos[Estado final],"Activo")+COUNTIFS(T_Prestamos[Estado final],"Judicializado")</f>
-        <v>3</v>
-      </c>
-      <c r="E69" s="93"/>
+      <c r="B69" s="125" t="s">
+        <v>132</v>
+      </c>
+      <c r="C69" s="125" t="s">
+        <v>142</v>
+      </c>
+      <c r="D69" s="93">
+        <f>COUNTIFS(T_Prestamos[Estado final],"Activo")</f>
+        <v>1</v>
+      </c>
+      <c r="E69" s="125"/>
       <c r="F69" s="49"/>
       <c r="G69" s="49"/>
     </row>
     <row r="70" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A70" s="92" t="s">
-        <v>142</v>
-      </c>
-      <c r="B70" s="93" t="s">
-        <v>136</v>
-      </c>
-      <c r="C70" s="93" t="s">
+      <c r="A70" s="122" t="s">
         <v>143</v>
       </c>
-      <c r="D70" s="91">
-        <f>COUNTIFS(T_Prestamos[Estado final],"Judicializado")</f>
-        <v>1</v>
-      </c>
-      <c r="E70" s="93"/>
+      <c r="B70" s="123" t="s">
+        <v>144</v>
+      </c>
+      <c r="C70" s="123" t="s">
+        <v>145</v>
+      </c>
+      <c r="D70" s="86">
+        <f>C44</f>
+        <v>450000</v>
+      </c>
+      <c r="E70" s="123"/>
       <c r="F70" s="49"/>
       <c r="G70" s="49"/>
     </row>
     <row r="71" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A71" s="101" t="s">
-        <v>145</v>
-      </c>
-      <c r="B71" s="102" t="s">
-        <v>136</v>
-      </c>
-      <c r="C71" s="102" t="s">
+      <c r="A71" s="122" t="s">
         <v>146</v>
       </c>
-      <c r="D71" s="103">
-        <f>COUNTIFS(T_Prestamos[Estado final],"Activo")</f>
-        <v>2</v>
-      </c>
-      <c r="E71" s="102"/>
+      <c r="B71" s="123" t="s">
+        <v>144</v>
+      </c>
+      <c r="C71" s="123" t="s">
+        <v>147</v>
+      </c>
+      <c r="D71" s="87">
+        <f>D51/D70</f>
+        <v>0.29072008888888889</v>
+      </c>
+      <c r="E71" s="123"/>
       <c r="F71" s="49"/>
       <c r="G71" s="49"/>
     </row>
     <row r="72" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A72" s="92" t="s">
-        <v>147</v>
-      </c>
-      <c r="B72" s="93" t="s">
+      <c r="A72" s="122" t="s">
         <v>148</v>
       </c>
-      <c r="C72" s="93" t="s">
+      <c r="B72" s="123" t="s">
+        <v>144</v>
+      </c>
+      <c r="C72" s="123" t="s">
         <v>149</v>
       </c>
-      <c r="D72" s="87">
-        <f>C46</f>
-        <v>750000</v>
-      </c>
-      <c r="E72" s="93"/>
+      <c r="D72" s="86">
+        <f>C45</f>
+        <v>100000</v>
+      </c>
+      <c r="E72" s="123"/>
       <c r="F72" s="49"/>
       <c r="G72" s="49"/>
     </row>
     <row r="73" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A73" s="92" t="s">
+      <c r="A73" s="124" t="s">
         <v>150</v>
       </c>
-      <c r="B73" s="93" t="s">
-        <v>148</v>
-      </c>
-      <c r="C73" s="93" t="s">
+      <c r="B73" s="125" t="s">
+        <v>144</v>
+      </c>
+      <c r="C73" s="125" t="s">
         <v>151</v>
       </c>
-      <c r="D73" s="88">
-        <f>D53/D72</f>
-        <v>0.19006403999999999</v>
-      </c>
-      <c r="E73" s="93"/>
+      <c r="D73" s="91">
+        <f>(D55+D56)/D72</f>
+        <v>0.28392165000000003</v>
+      </c>
+      <c r="E73" s="125"/>
       <c r="F73" s="49"/>
       <c r="G73" s="49"/>
     </row>
     <row r="74" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A74" s="92" t="s">
+      <c r="A74" s="122" t="s">
         <v>152</v>
       </c>
-      <c r="B74" s="93" t="s">
-        <v>148</v>
-      </c>
-      <c r="C74" s="93" t="s">
+      <c r="B74" s="123" t="s">
         <v>153</v>
       </c>
-      <c r="D74" s="87">
-        <f>C47</f>
-        <v>100000</v>
-      </c>
-      <c r="E74" s="93"/>
+      <c r="C74" s="123" t="s">
+        <v>154</v>
+      </c>
+      <c r="D74" s="90">
+        <f>AVERAGEIFS(T_Prestamos[Meses],T_Prestamos[Estado final],"&lt;&gt;Cancelado")</f>
+        <v>12</v>
+      </c>
+      <c r="E74" s="123"/>
       <c r="F74" s="49"/>
       <c r="G74" s="49"/>
     </row>
     <row r="75" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A75" s="101" t="s">
-        <v>154</v>
-      </c>
-      <c r="B75" s="102" t="s">
-        <v>148</v>
-      </c>
-      <c r="C75" s="102" t="s">
+      <c r="A75" s="122" t="s">
         <v>155</v>
       </c>
-      <c r="D75" s="97">
-        <f>(D57+D58)/D74</f>
-        <v>0.19254160000000001</v>
-      </c>
-      <c r="E75" s="102"/>
+      <c r="B75" s="123" t="s">
+        <v>153</v>
+      </c>
+      <c r="C75" s="123" t="s">
+        <v>156</v>
+      </c>
+      <c r="D75" s="90">
+        <f>AVERAGEIFS(T_Prestamos[Meses],T_Prestamos[Estado final],"Activo")</f>
+        <v>7</v>
+      </c>
+      <c r="E75" s="123"/>
       <c r="F75" s="49"/>
       <c r="G75" s="49"/>
     </row>
-    <row r="76" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A76" s="92" t="s">
-        <v>156</v>
-      </c>
-      <c r="B76" s="93" t="s">
+    <row r="76" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A76" s="122" t="s">
         <v>157</v>
       </c>
-      <c r="C76" s="93" t="s">
+      <c r="B76" s="123" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" s="123" t="s">
         <v>158</v>
       </c>
-      <c r="D76" s="91">
-        <f>AVERAGEIFS(T_Prestamos[Meses],T_Prestamos[Estado final],"&lt;&gt;Cancelado")</f>
-        <v>11.333333333333334</v>
-      </c>
-      <c r="E76" s="93"/>
+      <c r="D76" s="90">
+        <f>IFERROR(AVERAGEIFS(T_Prestamos[Meses],T_Prestamos[Estado final],"Judicializado"),0)</f>
+        <v>17</v>
+      </c>
+      <c r="E76" s="123"/>
       <c r="F76" s="49"/>
       <c r="G76" s="49"/>
     </row>
-    <row r="77" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A77" s="92" t="s">
-        <v>159</v>
-      </c>
-      <c r="B77" s="93" t="s">
-        <v>157</v>
-      </c>
-      <c r="C77" s="93" t="s">
-        <v>160</v>
-      </c>
-      <c r="D77" s="91">
-        <f>AVERAGEIFS(T_Prestamos[Meses],T_Prestamos[Estado final],"Activo")</f>
-        <v>12</v>
-      </c>
-      <c r="E77" s="93"/>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="22"/>
+      <c r="B77" s="22"/>
+      <c r="C77" s="100"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
       <c r="F77" s="49"/>
       <c r="G77" s="49"/>
     </row>
-    <row r="78" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A78" s="92" t="s">
-        <v>161</v>
-      </c>
-      <c r="B78" s="93" t="s">
-        <v>157</v>
-      </c>
-      <c r="C78" s="93" t="s">
-        <v>162</v>
-      </c>
-      <c r="D78" s="91">
-        <f>AVERAGEIFS(T_Prestamos[Meses],T_Prestamos[Estado final],"Judicializado")</f>
-        <v>10</v>
-      </c>
-      <c r="E78" s="93"/>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F78" s="49"/>
       <c r="G78" s="49"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" s="22"/>
-      <c r="B79" s="22"/>
-      <c r="C79" s="110"/>
-      <c r="D79" s="22"/>
-      <c r="E79" s="22"/>
       <c r="F79" s="49"/>
       <c r="G79" s="49"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F80" s="49"/>
       <c r="G80" s="49"/>
-    </row>
-    <row r="81" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F81" s="49"/>
-      <c r="G81" s="49"/>
-    </row>
-    <row r="82" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F82" s="49"/>
-      <c r="G82" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6816,10 +7299,11 @@
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="3">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6834,7 +7318,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
@@ -6842,27 +7326,27 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="17" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
@@ -6870,22 +7354,22 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
@@ -6893,32 +7377,32 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
@@ -6926,22 +7410,22 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="17" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
@@ -6949,21 +7433,1600 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="17" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92668B0-6A49-5047-9A24-4834DA0E9EFE}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8" style="129" customWidth="1"/>
+    <col min="2" max="2" width="12" style="129" customWidth="1"/>
+    <col min="3" max="3" width="18" style="129" customWidth="1"/>
+    <col min="4" max="4" width="22" style="129" customWidth="1"/>
+    <col min="5" max="5" width="40" style="129" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="129"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="140" t="s">
+        <v>291</v>
+      </c>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="130" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="130" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="130" t="s">
+        <v>293</v>
+      </c>
+      <c r="D2" s="130" t="s">
+        <v>294</v>
+      </c>
+      <c r="E2" s="130" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="131" t="s">
+        <v>295</v>
+      </c>
+      <c r="B3" s="131" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" s="132">
+        <v>1234.56</v>
+      </c>
+      <c r="D3" s="133" t="s">
+        <v>297</v>
+      </c>
+      <c r="E3" s="134" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="131" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="131" t="s">
+        <v>296</v>
+      </c>
+      <c r="C4" s="132">
+        <v>-1234.56</v>
+      </c>
+      <c r="D4" s="133" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="134" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="131" t="s">
+        <v>302</v>
+      </c>
+      <c r="B5" s="131" t="s">
+        <v>296</v>
+      </c>
+      <c r="C5" s="132">
+        <v>0</v>
+      </c>
+      <c r="D5" s="133" t="s">
+        <v>303</v>
+      </c>
+      <c r="E5" s="134" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="131" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" s="131" t="s">
+        <v>296</v>
+      </c>
+      <c r="C6" s="132">
+        <v>1000000</v>
+      </c>
+      <c r="D6" s="133" t="s">
+        <v>306</v>
+      </c>
+      <c r="E6" s="134" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="131" t="s">
+        <v>308</v>
+      </c>
+      <c r="B7" s="131" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" s="132">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="133" t="s">
+        <v>309</v>
+      </c>
+      <c r="E7" s="134" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="131" t="s">
+        <v>311</v>
+      </c>
+      <c r="B8" s="131" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" s="132"/>
+      <c r="D8" s="133" t="s">
+        <v>312</v>
+      </c>
+      <c r="E8" s="134" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="131" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" s="131" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" s="132">
+        <v>1234.56</v>
+      </c>
+      <c r="D9" s="133" t="s">
+        <v>316</v>
+      </c>
+      <c r="E9" s="134" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="131" t="s">
+        <v>318</v>
+      </c>
+      <c r="B10" s="131" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" s="132">
+        <v>1000000</v>
+      </c>
+      <c r="D10" s="133" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="134" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="131" t="s">
+        <v>321</v>
+      </c>
+      <c r="B11" s="131" t="s">
+        <v>315</v>
+      </c>
+      <c r="C11" s="132"/>
+      <c r="D11" s="133" t="s">
+        <v>312</v>
+      </c>
+      <c r="E11" s="134" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="131" t="s">
+        <v>322</v>
+      </c>
+      <c r="B12" s="131" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" s="132">
+        <v>1234.56</v>
+      </c>
+      <c r="D12" s="133" t="s">
+        <v>324</v>
+      </c>
+      <c r="E12" s="134" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="131" t="s">
+        <v>326</v>
+      </c>
+      <c r="B13" s="131" t="s">
+        <v>323</v>
+      </c>
+      <c r="C13" s="132">
+        <v>-500</v>
+      </c>
+      <c r="D13" s="133" t="s">
+        <v>327</v>
+      </c>
+      <c r="E13" s="134" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="131" t="s">
+        <v>329</v>
+      </c>
+      <c r="B14" s="131" t="s">
+        <v>323</v>
+      </c>
+      <c r="C14" s="132"/>
+      <c r="D14" s="133" t="s">
+        <v>312</v>
+      </c>
+      <c r="E14" s="134" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="131" t="s">
+        <v>330</v>
+      </c>
+      <c r="B15" s="131" t="s">
+        <v>331</v>
+      </c>
+      <c r="C15" s="132">
+        <v>1234.56</v>
+      </c>
+      <c r="D15" s="133" t="s">
+        <v>332</v>
+      </c>
+      <c r="E15" s="134" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="131" t="s">
+        <v>334</v>
+      </c>
+      <c r="B16" s="131" t="s">
+        <v>331</v>
+      </c>
+      <c r="C16" s="132">
+        <v>-1234.56</v>
+      </c>
+      <c r="D16" s="133" t="s">
+        <v>335</v>
+      </c>
+      <c r="E16" s="134" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="131" t="s">
+        <v>336</v>
+      </c>
+      <c r="B17" s="131" t="s">
+        <v>331</v>
+      </c>
+      <c r="C17" s="132"/>
+      <c r="D17" s="133" t="s">
+        <v>312</v>
+      </c>
+      <c r="E17" s="134" t="s">
+        <v>313</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB697AD8-CBB5-1A42-93F1-A16E7D07A8F6}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8" style="129" customWidth="1"/>
+    <col min="2" max="2" width="22" style="129" customWidth="1"/>
+    <col min="3" max="3" width="35" style="129" customWidth="1"/>
+    <col min="4" max="4" width="18" style="129" customWidth="1"/>
+    <col min="5" max="5" width="28" style="129" customWidth="1"/>
+    <col min="6" max="6" width="35" style="129" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="129"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="140" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="130" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="130" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="130" t="s">
+        <v>338</v>
+      </c>
+      <c r="D2" s="130" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" s="130" t="s">
+        <v>339</v>
+      </c>
+      <c r="F2" s="130" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="B3" s="131" t="s">
+        <v>341</v>
+      </c>
+      <c r="C3" s="132" t="s">
+        <v>342</v>
+      </c>
+      <c r="D3" s="133">
+        <v>500</v>
+      </c>
+      <c r="E3" s="134" t="s">
+        <v>343</v>
+      </c>
+      <c r="F3" s="134" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="131" t="s">
+        <v>345</v>
+      </c>
+      <c r="B4" s="131" t="s">
+        <v>341</v>
+      </c>
+      <c r="C4" s="132" t="s">
+        <v>346</v>
+      </c>
+      <c r="D4" s="133">
+        <v>400</v>
+      </c>
+      <c r="E4" s="134" t="s">
+        <v>347</v>
+      </c>
+      <c r="F4" s="134" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="131" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" s="131" t="s">
+        <v>341</v>
+      </c>
+      <c r="C5" s="132" t="s">
+        <v>350</v>
+      </c>
+      <c r="D5" s="133">
+        <v>600</v>
+      </c>
+      <c r="E5" s="134" t="s">
+        <v>351</v>
+      </c>
+      <c r="F5" s="134" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="131" t="s">
+        <v>353</v>
+      </c>
+      <c r="B6" s="131" t="s">
+        <v>341</v>
+      </c>
+      <c r="C6" s="132" t="s">
+        <v>354</v>
+      </c>
+      <c r="D6" s="133">
+        <v>0</v>
+      </c>
+      <c r="E6" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="F6" s="134" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="131" t="s">
+        <v>357</v>
+      </c>
+      <c r="B7" s="131" t="s">
+        <v>358</v>
+      </c>
+      <c r="C7" s="132" t="s">
+        <v>359</v>
+      </c>
+      <c r="D7" s="133">
+        <v>115.07</v>
+      </c>
+      <c r="E7" s="134" t="s">
+        <v>360</v>
+      </c>
+      <c r="F7" s="134" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="131" t="s">
+        <v>362</v>
+      </c>
+      <c r="B8" s="131" t="s">
+        <v>358</v>
+      </c>
+      <c r="C8" s="132" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" s="133">
+        <v>0</v>
+      </c>
+      <c r="E8" s="134" t="s">
+        <v>364</v>
+      </c>
+      <c r="F8" s="134" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="131" t="s">
+        <v>366</v>
+      </c>
+      <c r="B9" s="131" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" s="132" t="s">
+        <v>367</v>
+      </c>
+      <c r="D9" s="133">
+        <v>1400</v>
+      </c>
+      <c r="E9" s="134" t="s">
+        <v>368</v>
+      </c>
+      <c r="F9" s="134" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="131" t="s">
+        <v>370</v>
+      </c>
+      <c r="B10" s="131" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" s="132" t="s">
+        <v>371</v>
+      </c>
+      <c r="D10" s="133">
+        <v>1232.8800000000001</v>
+      </c>
+      <c r="E10" s="134" t="s">
+        <v>372</v>
+      </c>
+      <c r="F10" s="134" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="131" t="s">
+        <v>374</v>
+      </c>
+      <c r="B11" s="131" t="s">
+        <v>375</v>
+      </c>
+      <c r="C11" s="132" t="s">
+        <v>376</v>
+      </c>
+      <c r="D11" s="133" t="s">
+        <v>377</v>
+      </c>
+      <c r="E11" s="134" t="s">
+        <v>378</v>
+      </c>
+      <c r="F11" s="134" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="131" t="s">
+        <v>380</v>
+      </c>
+      <c r="B12" s="131" t="s">
+        <v>375</v>
+      </c>
+      <c r="C12" s="132" t="s">
+        <v>381</v>
+      </c>
+      <c r="D12" s="133" t="s">
+        <v>382</v>
+      </c>
+      <c r="E12" s="134" t="s">
+        <v>383</v>
+      </c>
+      <c r="F12" s="134" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="131" t="s">
+        <v>385</v>
+      </c>
+      <c r="B13" s="131" t="s">
+        <v>375</v>
+      </c>
+      <c r="C13" s="132" t="s">
+        <v>386</v>
+      </c>
+      <c r="D13" s="133" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="134" t="s">
+        <v>312</v>
+      </c>
+      <c r="F13" s="134" t="s">
+        <v>387</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E4F6A3-0625-9544-860E-1921109565C4}">
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8" style="129" customWidth="1"/>
+    <col min="2" max="2" width="35" style="129" customWidth="1"/>
+    <col min="3" max="3" width="20" style="129" customWidth="1"/>
+    <col min="4" max="4" width="10" style="129" customWidth="1"/>
+    <col min="5" max="5" width="22" style="129" customWidth="1"/>
+    <col min="6" max="6" width="14" style="129" customWidth="1"/>
+    <col min="7" max="7" width="18" style="129" customWidth="1"/>
+    <col min="8" max="9" width="16" style="129" customWidth="1"/>
+    <col min="10" max="10" width="40" style="129" customWidth="1"/>
+    <col min="11" max="16384" width="8.83203125" style="129"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="140" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+    </row>
+    <row r="2" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="142" t="s">
+        <v>389</v>
+      </c>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="130" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>390</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>391</v>
+      </c>
+      <c r="F3" s="130" t="s">
+        <v>392</v>
+      </c>
+      <c r="G3" s="130" t="s">
+        <v>393</v>
+      </c>
+      <c r="H3" s="130" t="s">
+        <v>394</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>395</v>
+      </c>
+      <c r="J3" s="130" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="131" t="s">
+        <v>396</v>
+      </c>
+      <c r="B4" s="131" t="s">
+        <v>397</v>
+      </c>
+      <c r="C4" s="132" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="132">
+        <v>1</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>398</v>
+      </c>
+      <c r="F4" s="133">
+        <v>1</v>
+      </c>
+      <c r="G4" s="133">
+        <v>200</v>
+      </c>
+      <c r="H4" s="133">
+        <v>66.67</v>
+      </c>
+      <c r="I4" s="133">
+        <v>108</v>
+      </c>
+      <c r="J4" s="134" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="131" t="s">
+        <v>400</v>
+      </c>
+      <c r="B5" s="131" t="s">
+        <v>401</v>
+      </c>
+      <c r="C5" s="132" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="132">
+        <v>2</v>
+      </c>
+      <c r="E5" s="133" t="s">
+        <v>402</v>
+      </c>
+      <c r="F5" s="133">
+        <v>1</v>
+      </c>
+      <c r="G5" s="133">
+        <v>200</v>
+      </c>
+      <c r="H5" s="133">
+        <v>66.67</v>
+      </c>
+      <c r="I5" s="133">
+        <v>108</v>
+      </c>
+      <c r="J5" s="134" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="131" t="s">
+        <v>404</v>
+      </c>
+      <c r="B6" s="131" t="s">
+        <v>405</v>
+      </c>
+      <c r="C6" s="132" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="132">
+        <v>12</v>
+      </c>
+      <c r="E6" s="133" t="s">
+        <v>406</v>
+      </c>
+      <c r="F6" s="133">
+        <v>1</v>
+      </c>
+      <c r="G6" s="133">
+        <v>200</v>
+      </c>
+      <c r="H6" s="133">
+        <v>66.67</v>
+      </c>
+      <c r="I6" s="133">
+        <v>108</v>
+      </c>
+      <c r="J6" s="134" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="131" t="s">
+        <v>408</v>
+      </c>
+      <c r="B7" s="131" t="s">
+        <v>409</v>
+      </c>
+      <c r="C7" s="132" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="132">
+        <v>1</v>
+      </c>
+      <c r="E7" s="133" t="s">
+        <v>398</v>
+      </c>
+      <c r="F7" s="133">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="G7" s="133">
+        <v>66.67</v>
+      </c>
+      <c r="H7" s="133">
+        <v>22.22</v>
+      </c>
+      <c r="I7" s="133">
+        <v>36</v>
+      </c>
+      <c r="J7" s="134" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="131" t="s">
+        <v>412</v>
+      </c>
+      <c r="B8" s="131" t="s">
+        <v>413</v>
+      </c>
+      <c r="C8" s="132" t="s">
+        <v>410</v>
+      </c>
+      <c r="D8" s="132">
+        <v>2</v>
+      </c>
+      <c r="E8" s="133" t="s">
+        <v>402</v>
+      </c>
+      <c r="F8" s="133">
+        <v>1</v>
+      </c>
+      <c r="G8" s="133">
+        <v>200</v>
+      </c>
+      <c r="H8" s="133">
+        <v>66.67</v>
+      </c>
+      <c r="I8" s="133">
+        <v>108</v>
+      </c>
+      <c r="J8" s="134" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="131" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" s="131" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9" s="132" t="s">
+        <v>417</v>
+      </c>
+      <c r="D9" s="132">
+        <v>1</v>
+      </c>
+      <c r="E9" s="133" t="s">
+        <v>402</v>
+      </c>
+      <c r="F9" s="133">
+        <v>0</v>
+      </c>
+      <c r="G9" s="133">
+        <v>0</v>
+      </c>
+      <c r="H9" s="133">
+        <v>0</v>
+      </c>
+      <c r="I9" s="133">
+        <v>0</v>
+      </c>
+      <c r="J9" s="134" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="131" t="s">
+        <v>419</v>
+      </c>
+      <c r="B10" s="131" t="s">
+        <v>420</v>
+      </c>
+      <c r="C10" s="132" t="s">
+        <v>417</v>
+      </c>
+      <c r="D10" s="132">
+        <v>2</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>421</v>
+      </c>
+      <c r="F10" s="133">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="G10" s="133">
+        <v>166.67</v>
+      </c>
+      <c r="H10" s="133">
+        <v>55.56</v>
+      </c>
+      <c r="I10" s="133">
+        <v>90</v>
+      </c>
+      <c r="J10" s="134" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="131" t="s">
+        <v>423</v>
+      </c>
+      <c r="B11" s="131" t="s">
+        <v>424</v>
+      </c>
+      <c r="C11" s="132" t="s">
+        <v>417</v>
+      </c>
+      <c r="D11" s="132">
+        <v>3</v>
+      </c>
+      <c r="E11" s="133" t="s">
+        <v>425</v>
+      </c>
+      <c r="F11" s="133">
+        <v>1</v>
+      </c>
+      <c r="G11" s="133">
+        <v>200</v>
+      </c>
+      <c r="H11" s="133">
+        <v>66.67</v>
+      </c>
+      <c r="I11" s="133">
+        <v>108</v>
+      </c>
+      <c r="J11" s="134" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="131" t="s">
+        <v>427</v>
+      </c>
+      <c r="B12" s="131" t="s">
+        <v>428</v>
+      </c>
+      <c r="C12" s="132" t="s">
+        <v>429</v>
+      </c>
+      <c r="D12" s="132">
+        <v>5</v>
+      </c>
+      <c r="E12" s="133" t="s">
+        <v>430</v>
+      </c>
+      <c r="F12" s="133">
+        <v>1</v>
+      </c>
+      <c r="G12" s="133">
+        <v>200</v>
+      </c>
+      <c r="H12" s="133">
+        <v>66.67</v>
+      </c>
+      <c r="I12" s="133">
+        <v>108</v>
+      </c>
+      <c r="J12" s="134" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="131" t="s">
+        <v>432</v>
+      </c>
+      <c r="B13" s="131" t="s">
+        <v>433</v>
+      </c>
+      <c r="C13" s="132" t="s">
+        <v>429</v>
+      </c>
+      <c r="D13" s="132">
+        <v>6</v>
+      </c>
+      <c r="E13" s="133" t="s">
+        <v>434</v>
+      </c>
+      <c r="F13" s="133">
+        <v>1</v>
+      </c>
+      <c r="G13" s="133">
+        <v>200</v>
+      </c>
+      <c r="H13" s="133">
+        <v>66.67</v>
+      </c>
+      <c r="I13" s="133">
+        <v>108</v>
+      </c>
+      <c r="J13" s="134" t="s">
+        <v>435</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18EB9A29-0C26-6E4C-BF2B-0B0F78D0FB76}">
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8" style="129" customWidth="1"/>
+    <col min="2" max="2" width="45" style="129" customWidth="1"/>
+    <col min="3" max="3" width="35" style="129" customWidth="1"/>
+    <col min="4" max="4" width="25" style="129" customWidth="1"/>
+    <col min="5" max="5" width="10" style="129" customWidth="1"/>
+    <col min="6" max="7" width="15" style="129" customWidth="1"/>
+    <col min="8" max="9" width="13" style="129" customWidth="1"/>
+    <col min="10" max="10" width="35" style="129" customWidth="1"/>
+    <col min="11" max="16384" width="8.83203125" style="129"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="140" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+    </row>
+    <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="128"/>
+      <c r="B2" s="135" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="143">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="128"/>
+      <c r="B3" s="135" t="s">
+        <v>437</v>
+      </c>
+      <c r="C3" s="144">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="128"/>
+      <c r="B4" s="135" t="s">
+        <v>438</v>
+      </c>
+      <c r="C4" s="145">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="128"/>
+      <c r="C5" s="136"/>
+    </row>
+    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="128"/>
+      <c r="B6" s="135" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="144">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="128"/>
+      <c r="B7" s="135" t="s">
+        <v>439</v>
+      </c>
+      <c r="C7" s="144">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="128"/>
+      <c r="B8" s="135" t="s">
+        <v>440</v>
+      </c>
+      <c r="C8" s="144">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="128"/>
+    </row>
+    <row r="10" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="128"/>
+      <c r="B10" s="135" t="s">
+        <v>441</v>
+      </c>
+      <c r="C10" s="146">
+        <f>ROUND(C2*C3/12,2)</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="128"/>
+      <c r="B11" s="135" t="s">
+        <v>442</v>
+      </c>
+      <c r="C11" s="146">
+        <f>ROUND(C10*C6,2)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="128"/>
+      <c r="B12" s="135" t="s">
+        <v>443</v>
+      </c>
+      <c r="C12" s="146">
+        <f>ROUND(-C2*C6*C7/12,2)</f>
+        <v>-66.67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="128"/>
+      <c r="B13" s="135" t="s">
+        <v>444</v>
+      </c>
+      <c r="C13" s="146">
+        <f>ROUND(C11+C12,2)</f>
+        <v>133.33000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="128"/>
+      <c r="B14" s="135" t="s">
+        <v>440</v>
+      </c>
+      <c r="C14" s="146">
+        <f>ROUND(-C13*C8,2)</f>
+        <v>-25.33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="128"/>
+      <c r="B15" s="135" t="s">
+        <v>445</v>
+      </c>
+      <c r="C15" s="146">
+        <f>C13+C14</f>
+        <v>108.00000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="128"/>
+      <c r="B16" s="128"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="128"/>
+    </row>
+    <row r="17" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="128"/>
+      <c r="B17" s="128"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="128"/>
+    </row>
+    <row r="18" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="128"/>
+    </row>
+    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="128"/>
+    </row>
+    <row r="20" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="128"/>
+    </row>
+    <row r="21" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="128"/>
+    </row>
+    <row r="22" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="128"/>
+    </row>
+    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="128"/>
+    </row>
+    <row r="24" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="142" t="s">
+        <v>446</v>
+      </c>
+      <c r="B24" s="141"/>
+      <c r="C24" s="141"/>
+      <c r="D24" s="141"/>
+      <c r="E24" s="141"/>
+      <c r="F24" s="141"/>
+      <c r="G24" s="141"/>
+      <c r="H24" s="141"/>
+      <c r="I24" s="141"/>
+      <c r="J24" s="141"/>
+      <c r="K24" s="141"/>
+    </row>
+    <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="130" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="130" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="130" t="s">
+        <v>447</v>
+      </c>
+      <c r="D25" s="130" t="s">
+        <v>448</v>
+      </c>
+      <c r="E25" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="130" t="s">
+        <v>449</v>
+      </c>
+      <c r="G25" s="130" t="s">
+        <v>450</v>
+      </c>
+      <c r="H25" s="130" t="s">
+        <v>451</v>
+      </c>
+      <c r="I25" s="130" t="s">
+        <v>452</v>
+      </c>
+      <c r="J25" s="130" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="131" t="s">
+        <v>374</v>
+      </c>
+      <c r="B26" s="131" t="s">
+        <v>453</v>
+      </c>
+      <c r="C26" s="132" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="132" t="s">
+        <v>454</v>
+      </c>
+      <c r="E26" s="132">
+        <v>1</v>
+      </c>
+      <c r="F26" s="147">
+        <f>$C$15</f>
+        <v>108.00000000000001</v>
+      </c>
+      <c r="G26" s="148">
+        <v>0</v>
+      </c>
+      <c r="H26" s="148">
+        <v>0</v>
+      </c>
+      <c r="I26" s="133" t="s">
+        <v>455</v>
+      </c>
+      <c r="J26" s="134" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="131" t="s">
+        <v>380</v>
+      </c>
+      <c r="B27" s="131" t="s">
+        <v>457</v>
+      </c>
+      <c r="C27" s="132" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="132" t="s">
+        <v>454</v>
+      </c>
+      <c r="E27" s="132">
+        <v>3</v>
+      </c>
+      <c r="F27" s="147">
+        <f>$C$15</f>
+        <v>108.00000000000001</v>
+      </c>
+      <c r="G27" s="148">
+        <v>0</v>
+      </c>
+      <c r="H27" s="148">
+        <v>0</v>
+      </c>
+      <c r="I27" s="133" t="s">
+        <v>455</v>
+      </c>
+      <c r="J27" s="134" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="131" t="s">
+        <v>385</v>
+      </c>
+      <c r="B28" s="131" t="s">
+        <v>459</v>
+      </c>
+      <c r="C28" s="132" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" s="132" t="s">
+        <v>454</v>
+      </c>
+      <c r="E28" s="132">
+        <v>1</v>
+      </c>
+      <c r="F28" s="148">
+        <v>0</v>
+      </c>
+      <c r="G28" s="147">
+        <f>$C$15</f>
+        <v>108.00000000000001</v>
+      </c>
+      <c r="H28" s="148">
+        <v>0</v>
+      </c>
+      <c r="I28" s="133" t="s">
+        <v>461</v>
+      </c>
+      <c r="J28" s="134" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="131" t="s">
+        <v>463</v>
+      </c>
+      <c r="B29" s="131" t="s">
+        <v>464</v>
+      </c>
+      <c r="C29" s="132" t="s">
+        <v>465</v>
+      </c>
+      <c r="D29" s="132" t="s">
+        <v>454</v>
+      </c>
+      <c r="E29" s="132">
+        <v>2</v>
+      </c>
+      <c r="F29" s="148">
+        <v>0</v>
+      </c>
+      <c r="G29" s="147">
+        <f>$C$15</f>
+        <v>108.00000000000001</v>
+      </c>
+      <c r="H29" s="148">
+        <v>0</v>
+      </c>
+      <c r="I29" s="133" t="s">
+        <v>461</v>
+      </c>
+      <c r="J29" s="134" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="131" t="s">
+        <v>467</v>
+      </c>
+      <c r="B30" s="131" t="s">
+        <v>468</v>
+      </c>
+      <c r="C30" s="132" t="s">
+        <v>469</v>
+      </c>
+      <c r="D30" s="132" t="s">
+        <v>470</v>
+      </c>
+      <c r="E30" s="132">
+        <v>1</v>
+      </c>
+      <c r="F30" s="148">
+        <v>0</v>
+      </c>
+      <c r="G30" s="148">
+        <v>0</v>
+      </c>
+      <c r="H30" s="147">
+        <f>$C$15</f>
+        <v>108.00000000000001</v>
+      </c>
+      <c r="I30" s="133" t="s">
+        <v>471</v>
+      </c>
+      <c r="J30" s="134" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="131" t="s">
+        <v>473</v>
+      </c>
+      <c r="B31" s="131" t="s">
+        <v>474</v>
+      </c>
+      <c r="C31" s="132" t="s">
+        <v>469</v>
+      </c>
+      <c r="D31" s="132" t="s">
+        <v>475</v>
+      </c>
+      <c r="E31" s="132">
+        <v>1</v>
+      </c>
+      <c r="F31" s="148">
+        <v>0</v>
+      </c>
+      <c r="G31" s="147">
+        <f>$C$15-H31</f>
+        <v>58.000000000000014</v>
+      </c>
+      <c r="H31" s="148">
+        <v>50</v>
+      </c>
+      <c r="I31" s="133" t="s">
+        <v>476</v>
+      </c>
+      <c r="J31" s="134" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="131" t="s">
+        <v>478</v>
+      </c>
+      <c r="B32" s="131" t="s">
+        <v>479</v>
+      </c>
+      <c r="C32" s="132" t="s">
+        <v>480</v>
+      </c>
+      <c r="D32" s="132" t="s">
+        <v>470</v>
+      </c>
+      <c r="E32" s="132">
+        <v>1</v>
+      </c>
+      <c r="F32" s="148">
+        <v>0</v>
+      </c>
+      <c r="G32" s="148">
+        <v>0</v>
+      </c>
+      <c r="H32" s="147">
+        <f>$C$15</f>
+        <v>108.00000000000001</v>
+      </c>
+      <c r="I32" s="133" t="s">
+        <v>471</v>
+      </c>
+      <c r="J32" s="134" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="131" t="s">
+        <v>482</v>
+      </c>
+      <c r="B33" s="131" t="s">
+        <v>479</v>
+      </c>
+      <c r="C33" s="132" t="s">
+        <v>480</v>
+      </c>
+      <c r="D33" s="132" t="s">
+        <v>470</v>
+      </c>
+      <c r="E33" s="132">
+        <v>2</v>
+      </c>
+      <c r="F33" s="148">
+        <v>0</v>
+      </c>
+      <c r="G33" s="147">
+        <f>$C$15</f>
+        <v>108.00000000000001</v>
+      </c>
+      <c r="H33" s="148">
+        <v>0</v>
+      </c>
+      <c r="I33" s="133" t="s">
+        <v>461</v>
+      </c>
+      <c r="J33" s="134" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="131" t="s">
+        <v>484</v>
+      </c>
+      <c r="B34" s="131" t="s">
+        <v>485</v>
+      </c>
+      <c r="C34" s="132" t="s">
+        <v>480</v>
+      </c>
+      <c r="D34" s="132" t="s">
+        <v>486</v>
+      </c>
+      <c r="E34" s="132">
+        <v>1</v>
+      </c>
+      <c r="F34" s="148">
+        <v>0</v>
+      </c>
+      <c r="G34" s="148">
+        <v>0</v>
+      </c>
+      <c r="H34" s="147">
+        <f>$C$15</f>
+        <v>108.00000000000001</v>
+      </c>
+      <c r="I34" s="133" t="s">
+        <v>471</v>
+      </c>
+      <c r="J34" s="134" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="131" t="s">
+        <v>488</v>
+      </c>
+      <c r="B35" s="131" t="s">
+        <v>489</v>
+      </c>
+      <c r="C35" s="132" t="s">
+        <v>480</v>
+      </c>
+      <c r="D35" s="132" t="s">
+        <v>486</v>
+      </c>
+      <c r="E35" s="132">
+        <v>2</v>
+      </c>
+      <c r="F35" s="148">
+        <v>0</v>
+      </c>
+      <c r="G35" s="148">
+        <v>0</v>
+      </c>
+      <c r="H35" s="147">
+        <f>$C$15</f>
+        <v>108.00000000000001</v>
+      </c>
+      <c r="I35" s="133" t="s">
+        <v>471</v>
+      </c>
+      <c r="J35" s="134" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="131" t="s">
+        <v>491</v>
+      </c>
+      <c r="B36" s="131" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="132" t="s">
+        <v>493</v>
+      </c>
+      <c r="D36" s="132" t="s">
+        <v>454</v>
+      </c>
+      <c r="E36" s="132">
+        <v>1</v>
+      </c>
+      <c r="F36" s="147">
+        <f>$C$15*50%</f>
+        <v>54.000000000000007</v>
+      </c>
+      <c r="G36" s="147">
+        <f>$C$15*50%</f>
+        <v>54.000000000000007</v>
+      </c>
+      <c r="H36" s="148">
+        <v>0</v>
+      </c>
+      <c r="I36" s="133" t="s">
+        <v>476</v>
+      </c>
+      <c r="J36" s="134" t="s">
+        <v>494</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A24:K24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>